--- a/development/one_file_rosetta_output/SP102957_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP102957_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E661"/>
+  <dimension ref="A1:F661"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
+        <v>10</v>
+      </c>
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -508,9 +517,12 @@
         </is>
       </c>
       <c r="D3" s="4">
+        <v>10</v>
+      </c>
+      <c r="E3" s="4">
         <v>2</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,9 +576,12 @@
         </is>
       </c>
       <c r="D4" s="4">
+        <v>10</v>
+      </c>
+      <c r="E4" s="4">
         <v>3</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -620,9 +635,12 @@
         </is>
       </c>
       <c r="D5" s="4">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4">
         <v>4</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -676,9 +694,12 @@
         </is>
       </c>
       <c r="D6" s="4">
+        <v>10</v>
+      </c>
+      <c r="E6" s="4">
         <v>5</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -734,7 +755,10 @@
       <c r="D7" s="4">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="4">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -760,9 +784,12 @@
         </is>
       </c>
       <c r="D8" s="4">
+        <v>10</v>
+      </c>
+      <c r="E8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -816,9 +843,12 @@
         </is>
       </c>
       <c r="D9" s="4">
+        <v>10</v>
+      </c>
+      <c r="E9" s="4">
         <v>2</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -872,9 +902,12 @@
         </is>
       </c>
       <c r="D10" s="4">
+        <v>10</v>
+      </c>
+      <c r="E10" s="4">
         <v>3</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -928,9 +961,12 @@
         </is>
       </c>
       <c r="D11" s="4">
+        <v>10</v>
+      </c>
+      <c r="E11" s="4">
         <v>4</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -984,9 +1020,12 @@
         </is>
       </c>
       <c r="D12" s="4">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4">
         <v>5</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1040,9 +1079,12 @@
         </is>
       </c>
       <c r="D13" s="4">
+        <v>9</v>
+      </c>
+      <c r="E13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1103,9 +1145,12 @@
         </is>
       </c>
       <c r="D14" s="4">
+        <v>9</v>
+      </c>
+      <c r="E14" s="4">
         <v>2</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1166,9 +1211,12 @@
         </is>
       </c>
       <c r="D15" s="4">
+        <v>9</v>
+      </c>
+      <c r="E15" s="4">
         <v>3</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1229,9 +1277,12 @@
         </is>
       </c>
       <c r="D16" s="4">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4">
         <v>4</v>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1292,9 +1343,12 @@
         </is>
       </c>
       <c r="D17" s="4">
+        <v>9</v>
+      </c>
+      <c r="E17" s="4">
         <v>5</v>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1355,9 +1409,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>2</v>
+      </c>
+      <c r="E18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1418,9 +1475,12 @@
         </is>
       </c>
       <c r="D19" s="4">
+        <v>4</v>
+      </c>
+      <c r="E19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1481,9 +1541,12 @@
         </is>
       </c>
       <c r="D20" s="4">
+        <v>4</v>
+      </c>
+      <c r="E20" s="4">
         <v>2</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1544,9 +1607,12 @@
         </is>
       </c>
       <c r="D21" s="4">
+        <v>4</v>
+      </c>
+      <c r="E21" s="4">
         <v>3</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1609,7 +1675,10 @@
       <c r="D22" s="4">
         <v>4</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>4</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1670,9 +1739,12 @@
         </is>
       </c>
       <c r="D23" s="4">
+        <v>10</v>
+      </c>
+      <c r="E23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1741,9 +1813,12 @@
         </is>
       </c>
       <c r="D24" s="4">
+        <v>10</v>
+      </c>
+      <c r="E24" s="4">
         <v>2</v>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1812,9 +1887,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>10</v>
+      </c>
+      <c r="E25" s="4">
         <v>3</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1883,9 +1961,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>10</v>
+      </c>
+      <c r="E26" s="4">
         <v>4</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1954,9 +2035,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>10</v>
+      </c>
+      <c r="E27" s="4">
         <v>5</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2025,9 +2109,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2096,9 +2183,12 @@
         </is>
       </c>
       <c r="D29" s="4">
+        <v>7</v>
+      </c>
+      <c r="E29" s="4">
         <v>2</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2167,9 +2257,12 @@
         </is>
       </c>
       <c r="D30" s="4">
+        <v>7</v>
+      </c>
+      <c r="E30" s="4">
         <v>3</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2238,9 +2331,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4">
         <v>4</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2309,9 +2405,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>4</v>
+      </c>
+      <c r="E32" s="4">
         <v>1</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2387,9 +2486,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>4</v>
+      </c>
+      <c r="E33" s="4">
         <v>2</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2465,9 +2567,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>4</v>
+      </c>
+      <c r="E34" s="4">
         <v>3</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2543,9 +2648,12 @@
         </is>
       </c>
       <c r="D35" s="4">
+        <v>4</v>
+      </c>
+      <c r="E35" s="4">
         <v>1</v>
       </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2621,9 +2729,12 @@
         </is>
       </c>
       <c r="D36" s="4">
+        <v>4</v>
+      </c>
+      <c r="E36" s="4">
         <v>2</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2699,9 +2810,12 @@
         </is>
       </c>
       <c r="D37" s="4">
+        <v>4</v>
+      </c>
+      <c r="E37" s="4">
         <v>3</v>
       </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2779,7 +2893,10 @@
       <c r="D38" s="4">
         <v>1</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2807,7 +2924,10 @@
       <c r="D39" s="4">
         <v>1</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2891,9 +3011,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>2</v>
+      </c>
+      <c r="E40" s="4">
         <v>1</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2979,7 +3102,10 @@
       <c r="D41" s="4">
         <v>2</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="E41" s="4">
+        <v>2</v>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3065,7 +3191,10 @@
       <c r="D42" s="4">
         <v>1</v>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3093,7 +3222,10 @@
       <c r="D43" s="4">
         <v>1</v>
       </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3186,7 +3318,10 @@
       <c r="D44" s="4">
         <v>1</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E44" s="4">
+        <v>1</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3212,9 +3347,12 @@
         </is>
       </c>
       <c r="D45" s="4">
+        <v>5</v>
+      </c>
+      <c r="E45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3268,9 +3406,12 @@
         </is>
       </c>
       <c r="D46" s="4">
+        <v>5</v>
+      </c>
+      <c r="E46" s="4">
         <v>2</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3324,9 +3465,12 @@
         </is>
       </c>
       <c r="D47" s="4">
+        <v>6</v>
+      </c>
+      <c r="E47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3380,9 +3524,12 @@
         </is>
       </c>
       <c r="D48" s="4">
+        <v>6</v>
+      </c>
+      <c r="E48" s="4">
         <v>2</v>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3436,9 +3583,12 @@
         </is>
       </c>
       <c r="D49" s="4">
+        <v>6</v>
+      </c>
+      <c r="E49" s="4">
         <v>3</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3492,9 +3642,12 @@
         </is>
       </c>
       <c r="D50" s="4">
+        <v>6</v>
+      </c>
+      <c r="E50" s="4">
         <v>4</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3548,9 +3701,12 @@
         </is>
       </c>
       <c r="D51" s="4">
+        <v>14</v>
+      </c>
+      <c r="E51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3611,9 +3767,12 @@
         </is>
       </c>
       <c r="D52" s="4">
+        <v>14</v>
+      </c>
+      <c r="E52" s="4">
         <v>2</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3674,9 +3833,12 @@
         </is>
       </c>
       <c r="D53" s="4">
+        <v>14</v>
+      </c>
+      <c r="E53" s="4">
         <v>3</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3737,9 +3899,12 @@
         </is>
       </c>
       <c r="D54" s="4">
+        <v>14</v>
+      </c>
+      <c r="E54" s="4">
         <v>4</v>
       </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3800,9 +3965,12 @@
         </is>
       </c>
       <c r="D55" s="4">
+        <v>14</v>
+      </c>
+      <c r="E55" s="4">
         <v>5</v>
       </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3865,7 +4033,10 @@
       <c r="D56" s="4">
         <v>1</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3926,9 +4097,12 @@
         </is>
       </c>
       <c r="D57" s="4">
+        <v>11</v>
+      </c>
+      <c r="E57" s="4">
         <v>1</v>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3989,9 +4163,12 @@
         </is>
       </c>
       <c r="D58" s="4">
+        <v>11</v>
+      </c>
+      <c r="E58" s="4">
         <v>2</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4052,9 +4229,12 @@
         </is>
       </c>
       <c r="D59" s="4">
+        <v>11</v>
+      </c>
+      <c r="E59" s="4">
         <v>3</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4115,9 +4295,12 @@
         </is>
       </c>
       <c r="D60" s="4">
+        <v>11</v>
+      </c>
+      <c r="E60" s="4">
         <v>4</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4178,9 +4361,12 @@
         </is>
       </c>
       <c r="D61" s="4">
+        <v>11</v>
+      </c>
+      <c r="E61" s="4">
         <v>5</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4241,9 +4427,12 @@
         </is>
       </c>
       <c r="D62" s="4">
+        <v>3</v>
+      </c>
+      <c r="E62" s="4">
         <v>1</v>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4271,7 +4460,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4297,9 +4489,12 @@
         </is>
       </c>
       <c r="D64" s="4">
+        <v>3</v>
+      </c>
+      <c r="E64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4368,9 +4563,12 @@
         </is>
       </c>
       <c r="D65" s="4">
+        <v>2</v>
+      </c>
+      <c r="E65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4448,7 +4646,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4524,9 +4725,12 @@
         </is>
       </c>
       <c r="D67" s="4">
+        <v>7</v>
+      </c>
+      <c r="E67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4602,9 +4806,12 @@
         </is>
       </c>
       <c r="D68" s="4">
+        <v>7</v>
+      </c>
+      <c r="E68" s="4">
         <v>2</v>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4680,9 +4887,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>7</v>
+      </c>
+      <c r="E69" s="4">
         <v>3</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4758,9 +4968,12 @@
         </is>
       </c>
       <c r="D70" s="4">
+        <v>7</v>
+      </c>
+      <c r="E70" s="4">
         <v>4</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4838,7 +5051,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4866,7 +5082,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4892,9 +5111,12 @@
         </is>
       </c>
       <c r="D73" s="4">
+        <v>2</v>
+      </c>
+      <c r="E73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4922,7 +5144,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4948,9 +5173,12 @@
         </is>
       </c>
       <c r="D75" s="4">
+        <v>15</v>
+      </c>
+      <c r="E75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5004,9 +5232,12 @@
         </is>
       </c>
       <c r="D76" s="4">
+        <v>15</v>
+      </c>
+      <c r="E76" s="4">
         <v>2</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5060,9 +5291,12 @@
         </is>
       </c>
       <c r="D77" s="4">
+        <v>15</v>
+      </c>
+      <c r="E77" s="4">
         <v>3</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5116,9 +5350,12 @@
         </is>
       </c>
       <c r="D78" s="4">
+        <v>15</v>
+      </c>
+      <c r="E78" s="4">
         <v>4</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5172,9 +5409,12 @@
         </is>
       </c>
       <c r="D79" s="4">
+        <v>15</v>
+      </c>
+      <c r="E79" s="4">
         <v>5</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5228,9 +5468,12 @@
         </is>
       </c>
       <c r="D80" s="4">
+        <v>4</v>
+      </c>
+      <c r="E80" s="4">
         <v>1</v>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5284,9 +5527,12 @@
         </is>
       </c>
       <c r="D81" s="4">
+        <v>4</v>
+      </c>
+      <c r="E81" s="4">
         <v>2</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5340,9 +5586,12 @@
         </is>
       </c>
       <c r="D82" s="4">
+        <v>11</v>
+      </c>
+      <c r="E82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5396,9 +5645,12 @@
         </is>
       </c>
       <c r="D83" s="4">
+        <v>11</v>
+      </c>
+      <c r="E83" s="4">
         <v>2</v>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5452,9 +5704,12 @@
         </is>
       </c>
       <c r="D84" s="4">
+        <v>11</v>
+      </c>
+      <c r="E84" s="4">
         <v>3</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5508,9 +5763,12 @@
         </is>
       </c>
       <c r="D85" s="4">
+        <v>11</v>
+      </c>
+      <c r="E85" s="4">
         <v>4</v>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5564,9 +5822,12 @@
         </is>
       </c>
       <c r="D86" s="4">
+        <v>11</v>
+      </c>
+      <c r="E86" s="4">
         <v>5</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5620,9 +5881,12 @@
         </is>
       </c>
       <c r="D87" s="4">
+        <v>37</v>
+      </c>
+      <c r="E87" s="4">
         <v>1</v>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5683,9 +5947,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>37</v>
+      </c>
+      <c r="E88" s="4">
         <v>2</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5746,9 +6013,12 @@
         </is>
       </c>
       <c r="D89" s="4">
+        <v>37</v>
+      </c>
+      <c r="E89" s="4">
         <v>3</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5809,9 +6079,12 @@
         </is>
       </c>
       <c r="D90" s="4">
+        <v>37</v>
+      </c>
+      <c r="E90" s="4">
         <v>4</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5872,9 +6145,12 @@
         </is>
       </c>
       <c r="D91" s="4">
+        <v>37</v>
+      </c>
+      <c r="E91" s="4">
         <v>5</v>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5935,9 +6211,12 @@
         </is>
       </c>
       <c r="D92" s="4">
+        <v>2</v>
+      </c>
+      <c r="E92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6000,7 +6279,10 @@
       <c r="D93" s="4">
         <v>2</v>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E93" s="4">
+        <v>2</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6061,9 +6343,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>39</v>
+      </c>
+      <c r="E94" s="4">
         <v>1</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6124,9 +6409,12 @@
         </is>
       </c>
       <c r="D95" s="4">
+        <v>39</v>
+      </c>
+      <c r="E95" s="4">
         <v>2</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6187,9 +6475,12 @@
         </is>
       </c>
       <c r="D96" s="4">
+        <v>39</v>
+      </c>
+      <c r="E96" s="4">
         <v>3</v>
       </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6250,9 +6541,12 @@
         </is>
       </c>
       <c r="D97" s="4">
+        <v>39</v>
+      </c>
+      <c r="E97" s="4">
         <v>4</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6313,9 +6607,12 @@
         </is>
       </c>
       <c r="D98" s="4">
+        <v>39</v>
+      </c>
+      <c r="E98" s="4">
         <v>5</v>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6376,9 +6673,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>12</v>
+      </c>
+      <c r="E99" s="4">
         <v>1</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6447,9 +6747,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>12</v>
+      </c>
+      <c r="E100" s="4">
         <v>2</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6518,9 +6821,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>12</v>
+      </c>
+      <c r="E101" s="4">
         <v>3</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6589,9 +6895,12 @@
         </is>
       </c>
       <c r="D102" s="4">
+        <v>12</v>
+      </c>
+      <c r="E102" s="4">
         <v>4</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6660,9 +6969,12 @@
         </is>
       </c>
       <c r="D103" s="4">
+        <v>12</v>
+      </c>
+      <c r="E103" s="4">
         <v>5</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6733,7 +7045,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6802,9 +7117,12 @@
         </is>
       </c>
       <c r="D105" s="4">
+        <v>18</v>
+      </c>
+      <c r="E105" s="4">
         <v>1</v>
       </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6873,9 +7191,12 @@
         </is>
       </c>
       <c r="D106" s="4">
+        <v>18</v>
+      </c>
+      <c r="E106" s="4">
         <v>2</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6944,9 +7265,12 @@
         </is>
       </c>
       <c r="D107" s="4">
+        <v>18</v>
+      </c>
+      <c r="E107" s="4">
         <v>3</v>
       </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7015,9 +7339,12 @@
         </is>
       </c>
       <c r="D108" s="4">
+        <v>18</v>
+      </c>
+      <c r="E108" s="4">
         <v>4</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7086,9 +7413,12 @@
         </is>
       </c>
       <c r="D109" s="4">
+        <v>18</v>
+      </c>
+      <c r="E109" s="4">
         <v>5</v>
       </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7157,9 +7487,12 @@
         </is>
       </c>
       <c r="D110" s="4">
+        <v>10</v>
+      </c>
+      <c r="E110" s="4">
         <v>1</v>
       </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7235,9 +7568,12 @@
         </is>
       </c>
       <c r="D111" s="4">
+        <v>10</v>
+      </c>
+      <c r="E111" s="4">
         <v>2</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7313,9 +7649,12 @@
         </is>
       </c>
       <c r="D112" s="4">
+        <v>10</v>
+      </c>
+      <c r="E112" s="4">
         <v>3</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7391,9 +7730,12 @@
         </is>
       </c>
       <c r="D113" s="4">
+        <v>10</v>
+      </c>
+      <c r="E113" s="4">
         <v>4</v>
       </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7469,9 +7811,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>10</v>
+      </c>
+      <c r="E114" s="4">
         <v>5</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7549,7 +7894,10 @@
       <c r="D115" s="4">
         <v>1</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E115" s="4">
+        <v>1</v>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -7575,9 +7923,12 @@
         </is>
       </c>
       <c r="D116" s="4">
+        <v>12</v>
+      </c>
+      <c r="E116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7653,9 +8004,12 @@
         </is>
       </c>
       <c r="D117" s="4">
+        <v>12</v>
+      </c>
+      <c r="E117" s="4">
         <v>2</v>
       </c>
-      <c r="E117" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7731,9 +8085,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>12</v>
+      </c>
+      <c r="E118" s="4">
         <v>3</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7809,9 +8166,12 @@
         </is>
       </c>
       <c r="D119" s="4">
+        <v>12</v>
+      </c>
+      <c r="E119" s="4">
         <v>4</v>
       </c>
-      <c r="E119" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7887,9 +8247,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>12</v>
+      </c>
+      <c r="E120" s="4">
         <v>5</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7967,7 +8330,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8053,7 +8419,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8079,9 +8448,12 @@
         </is>
       </c>
       <c r="D123" s="4">
+        <v>2</v>
+      </c>
+      <c r="E123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8107,9 +8479,12 @@
         </is>
       </c>
       <c r="D124" s="4">
+        <v>55</v>
+      </c>
+      <c r="E124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8163,9 +8538,12 @@
         </is>
       </c>
       <c r="D125" s="4">
+        <v>55</v>
+      </c>
+      <c r="E125" s="4">
         <v>2</v>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8219,9 +8597,12 @@
         </is>
       </c>
       <c r="D126" s="4">
+        <v>55</v>
+      </c>
+      <c r="E126" s="4">
         <v>3</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8275,9 +8656,12 @@
         </is>
       </c>
       <c r="D127" s="4">
+        <v>55</v>
+      </c>
+      <c r="E127" s="4">
         <v>4</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8331,9 +8715,12 @@
         </is>
       </c>
       <c r="D128" s="4">
+        <v>55</v>
+      </c>
+      <c r="E128" s="4">
         <v>5</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8387,9 +8774,12 @@
         </is>
       </c>
       <c r="D129" s="4">
+        <v>6</v>
+      </c>
+      <c r="E129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8443,9 +8833,12 @@
         </is>
       </c>
       <c r="D130" s="4">
+        <v>6</v>
+      </c>
+      <c r="E130" s="4">
         <v>2</v>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8499,9 +8892,12 @@
         </is>
       </c>
       <c r="D131" s="4">
+        <v>6</v>
+      </c>
+      <c r="E131" s="4">
         <v>3</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8555,9 +8951,12 @@
         </is>
       </c>
       <c r="D132" s="4">
+        <v>6</v>
+      </c>
+      <c r="E132" s="4">
         <v>4</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8611,9 +9010,12 @@
         </is>
       </c>
       <c r="D133" s="4">
+        <v>25</v>
+      </c>
+      <c r="E133" s="4">
         <v>1</v>
       </c>
-      <c r="E133" s="6" t="inlineStr">
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8667,9 +9069,12 @@
         </is>
       </c>
       <c r="D134" s="4">
+        <v>25</v>
+      </c>
+      <c r="E134" s="4">
         <v>2</v>
       </c>
-      <c r="E134" s="6" t="inlineStr">
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8723,9 +9128,12 @@
         </is>
       </c>
       <c r="D135" s="4">
+        <v>25</v>
+      </c>
+      <c r="E135" s="4">
         <v>3</v>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8779,9 +9187,12 @@
         </is>
       </c>
       <c r="D136" s="4">
+        <v>25</v>
+      </c>
+      <c r="E136" s="4">
         <v>4</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8835,9 +9246,12 @@
         </is>
       </c>
       <c r="D137" s="4">
+        <v>25</v>
+      </c>
+      <c r="E137" s="4">
         <v>5</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8891,9 +9305,12 @@
         </is>
       </c>
       <c r="D138" s="4">
+        <v>36</v>
+      </c>
+      <c r="E138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8954,9 +9371,12 @@
         </is>
       </c>
       <c r="D139" s="4">
+        <v>36</v>
+      </c>
+      <c r="E139" s="4">
         <v>2</v>
       </c>
-      <c r="E139" s="6" t="inlineStr">
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9017,9 +9437,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>36</v>
+      </c>
+      <c r="E140" s="4">
         <v>3</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9080,9 +9503,12 @@
         </is>
       </c>
       <c r="D141" s="4">
+        <v>36</v>
+      </c>
+      <c r="E141" s="4">
         <v>4</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9143,9 +9569,12 @@
         </is>
       </c>
       <c r="D142" s="4">
+        <v>36</v>
+      </c>
+      <c r="E142" s="4">
         <v>5</v>
       </c>
-      <c r="E142" s="6" t="inlineStr">
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9206,9 +9635,12 @@
         </is>
       </c>
       <c r="D143" s="4">
+        <v>8</v>
+      </c>
+      <c r="E143" s="4">
         <v>1</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9269,9 +9701,12 @@
         </is>
       </c>
       <c r="D144" s="4">
+        <v>8</v>
+      </c>
+      <c r="E144" s="4">
         <v>2</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9332,9 +9767,12 @@
         </is>
       </c>
       <c r="D145" s="4">
+        <v>8</v>
+      </c>
+      <c r="E145" s="4">
         <v>3</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9395,9 +9833,12 @@
         </is>
       </c>
       <c r="D146" s="4">
+        <v>8</v>
+      </c>
+      <c r="E146" s="4">
         <v>4</v>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9458,9 +9899,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>8</v>
+      </c>
+      <c r="E147" s="4">
         <v>5</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9521,9 +9965,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>15</v>
+      </c>
+      <c r="E148" s="4">
         <v>1</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9584,9 +10031,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>15</v>
+      </c>
+      <c r="E149" s="4">
         <v>2</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9647,9 +10097,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>15</v>
+      </c>
+      <c r="E150" s="4">
         <v>3</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9710,9 +10163,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>15</v>
+      </c>
+      <c r="E151" s="4">
         <v>4</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9773,9 +10229,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>15</v>
+      </c>
+      <c r="E152" s="4">
         <v>5</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9836,9 +10295,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>14</v>
+      </c>
+      <c r="E153" s="4">
         <v>1</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9907,9 +10369,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>14</v>
+      </c>
+      <c r="E154" s="4">
         <v>2</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9978,9 +10443,12 @@
         </is>
       </c>
       <c r="D155" s="4">
+        <v>14</v>
+      </c>
+      <c r="E155" s="4">
         <v>3</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10049,9 +10517,12 @@
         </is>
       </c>
       <c r="D156" s="4">
+        <v>14</v>
+      </c>
+      <c r="E156" s="4">
         <v>4</v>
       </c>
-      <c r="E156" s="6" t="inlineStr">
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10120,9 +10591,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>14</v>
+      </c>
+      <c r="E157" s="4">
         <v>5</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10191,9 +10665,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>18</v>
+      </c>
+      <c r="E158" s="4">
         <v>1</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10262,9 +10739,12 @@
         </is>
       </c>
       <c r="D159" s="4">
+        <v>18</v>
+      </c>
+      <c r="E159" s="4">
         <v>2</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10333,9 +10813,12 @@
         </is>
       </c>
       <c r="D160" s="4">
+        <v>18</v>
+      </c>
+      <c r="E160" s="4">
         <v>3</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10404,9 +10887,12 @@
         </is>
       </c>
       <c r="D161" s="4">
+        <v>18</v>
+      </c>
+      <c r="E161" s="4">
         <v>4</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10475,9 +10961,12 @@
         </is>
       </c>
       <c r="D162" s="4">
+        <v>18</v>
+      </c>
+      <c r="E162" s="4">
         <v>5</v>
       </c>
-      <c r="E162" s="6" t="inlineStr">
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10546,9 +11035,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>12</v>
+      </c>
+      <c r="E163" s="4">
         <v>1</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10617,9 +11109,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>12</v>
+      </c>
+      <c r="E164" s="4">
         <v>2</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10688,9 +11183,12 @@
         </is>
       </c>
       <c r="D165" s="4">
+        <v>12</v>
+      </c>
+      <c r="E165" s="4">
         <v>3</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10759,9 +11257,12 @@
         </is>
       </c>
       <c r="D166" s="4">
+        <v>12</v>
+      </c>
+      <c r="E166" s="4">
         <v>4</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10830,9 +11331,12 @@
         </is>
       </c>
       <c r="D167" s="4">
+        <v>12</v>
+      </c>
+      <c r="E167" s="4">
         <v>5</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10901,9 +11405,12 @@
         </is>
       </c>
       <c r="D168" s="4">
+        <v>15</v>
+      </c>
+      <c r="E168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10979,9 +11486,12 @@
         </is>
       </c>
       <c r="D169" s="4">
+        <v>15</v>
+      </c>
+      <c r="E169" s="4">
         <v>2</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11057,9 +11567,12 @@
         </is>
       </c>
       <c r="D170" s="4">
+        <v>15</v>
+      </c>
+      <c r="E170" s="4">
         <v>3</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11135,9 +11648,12 @@
         </is>
       </c>
       <c r="D171" s="4">
+        <v>15</v>
+      </c>
+      <c r="E171" s="4">
         <v>4</v>
       </c>
-      <c r="E171" s="6" t="inlineStr">
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11213,9 +11729,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>15</v>
+      </c>
+      <c r="E172" s="4">
         <v>5</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11291,9 +11810,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>6</v>
+      </c>
+      <c r="E173" s="4">
         <v>1</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11369,9 +11891,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>9</v>
+      </c>
+      <c r="E174" s="4">
         <v>1</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11447,9 +11972,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>9</v>
+      </c>
+      <c r="E175" s="4">
         <v>2</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11525,9 +12053,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>9</v>
+      </c>
+      <c r="E176" s="4">
         <v>3</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11603,9 +12134,12 @@
         </is>
       </c>
       <c r="D177" s="4">
+        <v>9</v>
+      </c>
+      <c r="E177" s="4">
         <v>4</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11681,9 +12215,12 @@
         </is>
       </c>
       <c r="D178" s="4">
+        <v>9</v>
+      </c>
+      <c r="E178" s="4">
         <v>5</v>
       </c>
-      <c r="E178" s="6" t="inlineStr">
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11759,9 +12296,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>9</v>
+      </c>
+      <c r="E179" s="4">
         <v>1</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11845,9 +12385,12 @@
         </is>
       </c>
       <c r="D180" s="4">
+        <v>9</v>
+      </c>
+      <c r="E180" s="4">
         <v>2</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11931,9 +12474,12 @@
         </is>
       </c>
       <c r="D181" s="4">
+        <v>9</v>
+      </c>
+      <c r="E181" s="4">
         <v>3</v>
       </c>
-      <c r="E181" s="6" t="inlineStr">
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12017,9 +12563,12 @@
         </is>
       </c>
       <c r="D182" s="4">
+        <v>9</v>
+      </c>
+      <c r="E182" s="4">
         <v>4</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12103,9 +12652,12 @@
         </is>
       </c>
       <c r="D183" s="4">
+        <v>9</v>
+      </c>
+      <c r="E183" s="4">
         <v>5</v>
       </c>
-      <c r="E183" s="6" t="inlineStr">
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12189,9 +12741,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>2</v>
+      </c>
+      <c r="E184" s="4">
         <v>1</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12275,9 +12830,12 @@
         </is>
       </c>
       <c r="D185" s="4">
+        <v>3</v>
+      </c>
+      <c r="E185" s="4">
         <v>1</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12361,9 +12919,12 @@
         </is>
       </c>
       <c r="D186" s="4">
+        <v>2</v>
+      </c>
+      <c r="E186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12454,9 +13015,12 @@
         </is>
       </c>
       <c r="D187" s="4">
+        <v>2</v>
+      </c>
+      <c r="E187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12547,9 +13111,12 @@
         </is>
       </c>
       <c r="D188" s="4">
+        <v>2</v>
+      </c>
+      <c r="E188" s="4">
         <v>1</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12642,7 +13209,10 @@
       <c r="D189" s="4">
         <v>2</v>
       </c>
-      <c r="E189" s="6" t="inlineStr">
+      <c r="E189" s="4">
+        <v>2</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12733,9 +13303,12 @@
         </is>
       </c>
       <c r="D190" s="4">
+        <v>3</v>
+      </c>
+      <c r="E190" s="4">
         <v>1</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12834,9 +13407,12 @@
         </is>
       </c>
       <c r="D191" s="4">
+        <v>3</v>
+      </c>
+      <c r="E191" s="4">
         <v>2</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12937,7 +13513,10 @@
       <c r="D192" s="4">
         <v>3</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>3</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13038,7 +13617,10 @@
       <c r="D193" s="4">
         <v>1</v>
       </c>
-      <c r="E193" s="6" t="inlineStr">
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13066,7 +13648,10 @@
       <c r="D194" s="4">
         <v>1</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="E194" s="4">
+        <v>1</v>
+      </c>
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13167,7 +13752,10 @@
       <c r="D195" s="4">
         <v>1</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="E195" s="4">
+        <v>1</v>
+      </c>
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13275,7 +13863,10 @@
       <c r="D196" s="4">
         <v>1</v>
       </c>
-      <c r="E196" s="6" t="inlineStr">
+      <c r="E196" s="4">
+        <v>1</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -13301,9 +13892,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>48</v>
+      </c>
+      <c r="E197" s="4">
         <v>1</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13357,9 +13951,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>48</v>
+      </c>
+      <c r="E198" s="4">
         <v>2</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13413,9 +14010,12 @@
         </is>
       </c>
       <c r="D199" s="4">
+        <v>48</v>
+      </c>
+      <c r="E199" s="4">
         <v>3</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13469,9 +14069,12 @@
         </is>
       </c>
       <c r="D200" s="4">
+        <v>48</v>
+      </c>
+      <c r="E200" s="4">
         <v>4</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13525,9 +14128,12 @@
         </is>
       </c>
       <c r="D201" s="4">
+        <v>48</v>
+      </c>
+      <c r="E201" s="4">
         <v>5</v>
       </c>
-      <c r="E201" s="6" t="inlineStr">
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13581,9 +14187,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>3</v>
+      </c>
+      <c r="E202" s="4">
         <v>1</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13637,9 +14246,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>19</v>
+      </c>
+      <c r="E203" s="4">
         <v>1</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13693,9 +14305,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>19</v>
+      </c>
+      <c r="E204" s="4">
         <v>2</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13749,9 +14364,12 @@
         </is>
       </c>
       <c r="D205" s="4">
+        <v>19</v>
+      </c>
+      <c r="E205" s="4">
         <v>3</v>
       </c>
-      <c r="E205" s="6" t="inlineStr">
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13805,9 +14423,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>19</v>
+      </c>
+      <c r="E206" s="4">
         <v>4</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13861,9 +14482,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>19</v>
+      </c>
+      <c r="E207" s="4">
         <v>5</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13917,9 +14541,12 @@
         </is>
       </c>
       <c r="D208" s="4">
+        <v>9</v>
+      </c>
+      <c r="E208" s="4">
         <v>1</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13980,9 +14607,12 @@
         </is>
       </c>
       <c r="D209" s="4">
+        <v>9</v>
+      </c>
+      <c r="E209" s="4">
         <v>2</v>
       </c>
-      <c r="E209" s="6" t="inlineStr">
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14043,9 +14673,12 @@
         </is>
       </c>
       <c r="D210" s="4">
+        <v>9</v>
+      </c>
+      <c r="E210" s="4">
         <v>3</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14106,9 +14739,12 @@
         </is>
       </c>
       <c r="D211" s="4">
+        <v>6</v>
+      </c>
+      <c r="E211" s="4">
         <v>1</v>
       </c>
-      <c r="E211" s="6" t="inlineStr">
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14169,9 +14805,12 @@
         </is>
       </c>
       <c r="D212" s="4">
+        <v>6</v>
+      </c>
+      <c r="E212" s="4">
         <v>2</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14232,9 +14871,12 @@
         </is>
       </c>
       <c r="D213" s="4">
+        <v>6</v>
+      </c>
+      <c r="E213" s="4">
         <v>3</v>
       </c>
-      <c r="E213" s="6" t="inlineStr">
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14295,9 +14937,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>6</v>
+      </c>
+      <c r="E214" s="4">
         <v>4</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14358,9 +15003,12 @@
         </is>
       </c>
       <c r="D215" s="4">
+        <v>9</v>
+      </c>
+      <c r="E215" s="4">
         <v>1</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14421,9 +15069,12 @@
         </is>
       </c>
       <c r="D216" s="4">
+        <v>9</v>
+      </c>
+      <c r="E216" s="4">
         <v>2</v>
       </c>
-      <c r="E216" s="6" t="inlineStr">
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14484,9 +15135,12 @@
         </is>
       </c>
       <c r="D217" s="4">
+        <v>9</v>
+      </c>
+      <c r="E217" s="4">
         <v>3</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14547,9 +15201,12 @@
         </is>
       </c>
       <c r="D218" s="4">
+        <v>9</v>
+      </c>
+      <c r="E218" s="4">
         <v>4</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14610,9 +15267,12 @@
         </is>
       </c>
       <c r="D219" s="4">
+        <v>5</v>
+      </c>
+      <c r="E219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14681,9 +15341,12 @@
         </is>
       </c>
       <c r="D220" s="4">
+        <v>5</v>
+      </c>
+      <c r="E220" s="4">
         <v>2</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14752,9 +15415,12 @@
         </is>
       </c>
       <c r="D221" s="4">
+        <v>5</v>
+      </c>
+      <c r="E221" s="4">
         <v>3</v>
       </c>
-      <c r="E221" s="6" t="inlineStr">
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14823,9 +15489,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>8</v>
+      </c>
+      <c r="E222" s="4">
         <v>1</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14894,9 +15563,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>8</v>
+      </c>
+      <c r="E223" s="4">
         <v>2</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14965,9 +15637,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>8</v>
+      </c>
+      <c r="E224" s="4">
         <v>3</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15036,9 +15711,12 @@
         </is>
       </c>
       <c r="D225" s="4">
+        <v>8</v>
+      </c>
+      <c r="E225" s="4">
         <v>4</v>
       </c>
-      <c r="E225" s="6" t="inlineStr">
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15107,9 +15785,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>8</v>
+      </c>
+      <c r="E226" s="4">
         <v>5</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15178,9 +15859,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>6</v>
+      </c>
+      <c r="E227" s="4">
         <v>1</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15249,9 +15933,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>5</v>
+      </c>
+      <c r="E228" s="4">
         <v>1</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15327,9 +16014,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>5</v>
+      </c>
+      <c r="E229" s="4">
         <v>2</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15405,9 +16095,12 @@
         </is>
       </c>
       <c r="D230" s="4">
+        <v>5</v>
+      </c>
+      <c r="E230" s="4">
         <v>3</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15483,9 +16176,12 @@
         </is>
       </c>
       <c r="D231" s="4">
+        <v>5</v>
+      </c>
+      <c r="E231" s="4">
         <v>1</v>
       </c>
-      <c r="E231" s="6" t="inlineStr">
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -15511,9 +16207,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>5</v>
+      </c>
+      <c r="E232" s="4">
         <v>1</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15589,9 +16288,12 @@
         </is>
       </c>
       <c r="D233" s="4">
+        <v>5</v>
+      </c>
+      <c r="E233" s="4">
         <v>2</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15667,9 +16369,12 @@
         </is>
       </c>
       <c r="D234" s="4">
+        <v>5</v>
+      </c>
+      <c r="E234" s="4">
         <v>1</v>
       </c>
-      <c r="E234" s="6" t="inlineStr">
+      <c r="F234" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15753,9 +16458,12 @@
         </is>
       </c>
       <c r="D235" s="4">
+        <v>5</v>
+      </c>
+      <c r="E235" s="4">
         <v>2</v>
       </c>
-      <c r="E235" s="6" t="inlineStr">
+      <c r="F235" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15839,9 +16547,12 @@
         </is>
       </c>
       <c r="D236" s="4">
+        <v>5</v>
+      </c>
+      <c r="E236" s="4">
         <v>3</v>
       </c>
-      <c r="E236" s="6" t="inlineStr">
+      <c r="F236" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15925,9 +16636,12 @@
         </is>
       </c>
       <c r="D237" s="4">
+        <v>5</v>
+      </c>
+      <c r="E237" s="4">
         <v>4</v>
       </c>
-      <c r="E237" s="6" t="inlineStr">
+      <c r="F237" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16011,9 +16725,12 @@
         </is>
       </c>
       <c r="D238" s="4">
+        <v>2</v>
+      </c>
+      <c r="E238" s="4">
         <v>1</v>
       </c>
-      <c r="E238" s="6" t="inlineStr">
+      <c r="F238" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16097,9 +16814,12 @@
         </is>
       </c>
       <c r="D239" s="4">
+        <v>3</v>
+      </c>
+      <c r="E239" s="4">
         <v>1</v>
       </c>
-      <c r="E239" s="6" t="inlineStr">
+      <c r="F239" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16183,9 +16903,12 @@
         </is>
       </c>
       <c r="D240" s="4">
+        <v>3</v>
+      </c>
+      <c r="E240" s="4">
         <v>2</v>
       </c>
-      <c r="E240" s="6" t="inlineStr">
+      <c r="F240" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16269,9 +16992,12 @@
         </is>
       </c>
       <c r="D241" s="4">
+        <v>3</v>
+      </c>
+      <c r="E241" s="4">
         <v>1</v>
       </c>
-      <c r="E241" s="6" t="inlineStr">
+      <c r="F241" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -16297,9 +17023,12 @@
         </is>
       </c>
       <c r="D242" s="4">
+        <v>3</v>
+      </c>
+      <c r="E242" s="4">
         <v>1</v>
       </c>
-      <c r="E242" s="6" t="inlineStr">
+      <c r="F242" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16390,9 +17119,12 @@
         </is>
       </c>
       <c r="D243" s="4">
+        <v>3</v>
+      </c>
+      <c r="E243" s="4">
         <v>2</v>
       </c>
-      <c r="E243" s="6" t="inlineStr">
+      <c r="F243" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16485,7 +17217,10 @@
       <c r="D244" s="4">
         <v>1</v>
       </c>
-      <c r="E244" s="6" t="inlineStr">
+      <c r="E244" s="4">
+        <v>1</v>
+      </c>
+      <c r="F244" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16586,7 +17321,10 @@
       <c r="D245" s="4">
         <v>1</v>
       </c>
-      <c r="E245" s="6" t="inlineStr">
+      <c r="E245" s="4">
+        <v>1</v>
+      </c>
+      <c r="F245" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16692,9 +17430,12 @@
         </is>
       </c>
       <c r="D246" s="4">
+        <v>38</v>
+      </c>
+      <c r="E246" s="4">
         <v>1</v>
       </c>
-      <c r="E246" s="6" t="inlineStr">
+      <c r="F246" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16748,9 +17489,12 @@
         </is>
       </c>
       <c r="D247" s="4">
+        <v>38</v>
+      </c>
+      <c r="E247" s="4">
         <v>2</v>
       </c>
-      <c r="E247" s="6" t="inlineStr">
+      <c r="F247" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16804,9 +17548,12 @@
         </is>
       </c>
       <c r="D248" s="4">
+        <v>38</v>
+      </c>
+      <c r="E248" s="4">
         <v>3</v>
       </c>
-      <c r="E248" s="6" t="inlineStr">
+      <c r="F248" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16860,9 +17607,12 @@
         </is>
       </c>
       <c r="D249" s="4">
+        <v>38</v>
+      </c>
+      <c r="E249" s="4">
         <v>4</v>
       </c>
-      <c r="E249" s="6" t="inlineStr">
+      <c r="F249" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16916,9 +17666,12 @@
         </is>
       </c>
       <c r="D250" s="4">
+        <v>38</v>
+      </c>
+      <c r="E250" s="4">
         <v>5</v>
       </c>
-      <c r="E250" s="6" t="inlineStr">
+      <c r="F250" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16972,9 +17725,12 @@
         </is>
       </c>
       <c r="D251" s="4">
+        <v>5</v>
+      </c>
+      <c r="E251" s="4">
         <v>1</v>
       </c>
-      <c r="E251" s="6" t="inlineStr">
+      <c r="F251" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17028,9 +17784,12 @@
         </is>
       </c>
       <c r="D252" s="4">
+        <v>5</v>
+      </c>
+      <c r="E252" s="4">
         <v>2</v>
       </c>
-      <c r="E252" s="6" t="inlineStr">
+      <c r="F252" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17084,9 +17843,12 @@
         </is>
       </c>
       <c r="D253" s="4">
+        <v>20</v>
+      </c>
+      <c r="E253" s="4">
         <v>1</v>
       </c>
-      <c r="E253" s="6" t="inlineStr">
+      <c r="F253" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17140,9 +17902,12 @@
         </is>
       </c>
       <c r="D254" s="4">
+        <v>20</v>
+      </c>
+      <c r="E254" s="4">
         <v>2</v>
       </c>
-      <c r="E254" s="6" t="inlineStr">
+      <c r="F254" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17196,9 +17961,12 @@
         </is>
       </c>
       <c r="D255" s="4">
+        <v>20</v>
+      </c>
+      <c r="E255" s="4">
         <v>3</v>
       </c>
-      <c r="E255" s="6" t="inlineStr">
+      <c r="F255" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17252,9 +18020,12 @@
         </is>
       </c>
       <c r="D256" s="4">
+        <v>20</v>
+      </c>
+      <c r="E256" s="4">
         <v>4</v>
       </c>
-      <c r="E256" s="6" t="inlineStr">
+      <c r="F256" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17308,9 +18079,12 @@
         </is>
       </c>
       <c r="D257" s="4">
+        <v>20</v>
+      </c>
+      <c r="E257" s="4">
         <v>5</v>
       </c>
-      <c r="E257" s="6" t="inlineStr">
+      <c r="F257" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17364,9 +18138,12 @@
         </is>
       </c>
       <c r="D258" s="4">
+        <v>17</v>
+      </c>
+      <c r="E258" s="4">
         <v>1</v>
       </c>
-      <c r="E258" s="6" t="inlineStr">
+      <c r="F258" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17427,9 +18204,12 @@
         </is>
       </c>
       <c r="D259" s="4">
+        <v>17</v>
+      </c>
+      <c r="E259" s="4">
         <v>2</v>
       </c>
-      <c r="E259" s="6" t="inlineStr">
+      <c r="F259" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17490,9 +18270,12 @@
         </is>
       </c>
       <c r="D260" s="4">
+        <v>17</v>
+      </c>
+      <c r="E260" s="4">
         <v>3</v>
       </c>
-      <c r="E260" s="6" t="inlineStr">
+      <c r="F260" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17553,9 +18336,12 @@
         </is>
       </c>
       <c r="D261" s="4">
+        <v>17</v>
+      </c>
+      <c r="E261" s="4">
         <v>4</v>
       </c>
-      <c r="E261" s="6" t="inlineStr">
+      <c r="F261" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17616,9 +18402,12 @@
         </is>
       </c>
       <c r="D262" s="4">
+        <v>17</v>
+      </c>
+      <c r="E262" s="4">
         <v>5</v>
       </c>
-      <c r="E262" s="6" t="inlineStr">
+      <c r="F262" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17679,9 +18468,12 @@
         </is>
       </c>
       <c r="D263" s="4">
+        <v>3</v>
+      </c>
+      <c r="E263" s="4">
         <v>1</v>
       </c>
-      <c r="E263" s="6" t="inlineStr">
+      <c r="F263" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17742,9 +18534,12 @@
         </is>
       </c>
       <c r="D264" s="4">
+        <v>3</v>
+      </c>
+      <c r="E264" s="4">
         <v>2</v>
       </c>
-      <c r="E264" s="6" t="inlineStr">
+      <c r="F264" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17805,9 +18600,12 @@
         </is>
       </c>
       <c r="D265" s="4">
+        <v>13</v>
+      </c>
+      <c r="E265" s="4">
         <v>1</v>
       </c>
-      <c r="E265" s="6" t="inlineStr">
+      <c r="F265" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17868,9 +18666,12 @@
         </is>
       </c>
       <c r="D266" s="4">
+        <v>13</v>
+      </c>
+      <c r="E266" s="4">
         <v>2</v>
       </c>
-      <c r="E266" s="6" t="inlineStr">
+      <c r="F266" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17931,9 +18732,12 @@
         </is>
       </c>
       <c r="D267" s="4">
+        <v>13</v>
+      </c>
+      <c r="E267" s="4">
         <v>3</v>
       </c>
-      <c r="E267" s="6" t="inlineStr">
+      <c r="F267" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -17994,9 +18798,12 @@
         </is>
       </c>
       <c r="D268" s="4">
+        <v>13</v>
+      </c>
+      <c r="E268" s="4">
         <v>4</v>
       </c>
-      <c r="E268" s="6" t="inlineStr">
+      <c r="F268" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18057,9 +18864,12 @@
         </is>
       </c>
       <c r="D269" s="4">
+        <v>13</v>
+      </c>
+      <c r="E269" s="4">
         <v>5</v>
       </c>
-      <c r="E269" s="6" t="inlineStr">
+      <c r="F269" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18120,9 +18930,12 @@
         </is>
       </c>
       <c r="D270" s="4">
+        <v>5</v>
+      </c>
+      <c r="E270" s="4">
         <v>1</v>
       </c>
-      <c r="E270" s="6" t="inlineStr">
+      <c r="F270" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18191,9 +19004,12 @@
         </is>
       </c>
       <c r="D271" s="4">
+        <v>5</v>
+      </c>
+      <c r="E271" s="4">
         <v>2</v>
       </c>
-      <c r="E271" s="6" t="inlineStr">
+      <c r="F271" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18262,9 +19078,12 @@
         </is>
       </c>
       <c r="D272" s="4">
+        <v>5</v>
+      </c>
+      <c r="E272" s="4">
         <v>3</v>
       </c>
-      <c r="E272" s="6" t="inlineStr">
+      <c r="F272" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18333,9 +19152,12 @@
         </is>
       </c>
       <c r="D273" s="4">
+        <v>7</v>
+      </c>
+      <c r="E273" s="4">
         <v>1</v>
       </c>
-      <c r="E273" s="6" t="inlineStr">
+      <c r="F273" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18361,9 +19183,12 @@
         </is>
       </c>
       <c r="D274" s="4">
+        <v>4</v>
+      </c>
+      <c r="E274" s="4">
         <v>1</v>
       </c>
-      <c r="E274" s="6" t="inlineStr">
+      <c r="F274" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18432,9 +19257,12 @@
         </is>
       </c>
       <c r="D275" s="4">
+        <v>4</v>
+      </c>
+      <c r="E275" s="4">
         <v>2</v>
       </c>
-      <c r="E275" s="6" t="inlineStr">
+      <c r="F275" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18505,7 +19333,10 @@
       <c r="D276" s="4">
         <v>1</v>
       </c>
-      <c r="E276" s="6" t="inlineStr">
+      <c r="E276" s="4">
+        <v>1</v>
+      </c>
+      <c r="F276" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18531,9 +19362,12 @@
         </is>
       </c>
       <c r="D277" s="4">
+        <v>4</v>
+      </c>
+      <c r="E277" s="4">
         <v>1</v>
       </c>
-      <c r="E277" s="6" t="inlineStr">
+      <c r="F277" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18609,9 +19443,12 @@
         </is>
       </c>
       <c r="D278" s="4">
+        <v>4</v>
+      </c>
+      <c r="E278" s="4">
         <v>2</v>
       </c>
-      <c r="E278" s="6" t="inlineStr">
+      <c r="F278" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18687,9 +19524,12 @@
         </is>
       </c>
       <c r="D279" s="4">
+        <v>4</v>
+      </c>
+      <c r="E279" s="4">
         <v>3</v>
       </c>
-      <c r="E279" s="6" t="inlineStr">
+      <c r="F279" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18765,9 +19605,12 @@
         </is>
       </c>
       <c r="D280" s="4">
+        <v>3</v>
+      </c>
+      <c r="E280" s="4">
         <v>1</v>
       </c>
-      <c r="E280" s="6" t="inlineStr">
+      <c r="F280" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18843,9 +19686,12 @@
         </is>
       </c>
       <c r="D281" s="4">
+        <v>2</v>
+      </c>
+      <c r="E281" s="4">
         <v>1</v>
       </c>
-      <c r="E281" s="6" t="inlineStr">
+      <c r="F281" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -18873,7 +19719,10 @@
       <c r="D282" s="4">
         <v>1</v>
       </c>
-      <c r="E282" s="6" t="inlineStr">
+      <c r="E282" s="4">
+        <v>1</v>
+      </c>
+      <c r="F282" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -18959,7 +19808,10 @@
       <c r="D283" s="4">
         <v>1</v>
       </c>
-      <c r="E283" s="6" t="inlineStr">
+      <c r="E283" s="4">
+        <v>1</v>
+      </c>
+      <c r="F283" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19020,9 +19872,12 @@
         </is>
       </c>
       <c r="D284" s="4">
+        <v>2</v>
+      </c>
+      <c r="E284" s="4">
         <v>1</v>
       </c>
-      <c r="E284" s="6" t="inlineStr">
+      <c r="F284" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19050,7 +19905,10 @@
       <c r="D285" s="4">
         <v>1</v>
       </c>
-      <c r="E285" s="6" t="inlineStr">
+      <c r="E285" s="4">
+        <v>1</v>
+      </c>
+      <c r="F285" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19078,7 +19936,10 @@
       <c r="D286" s="4">
         <v>1</v>
       </c>
-      <c r="E286" s="6" t="inlineStr">
+      <c r="E286" s="4">
+        <v>1</v>
+      </c>
+      <c r="F286" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19106,7 +19967,10 @@
       <c r="D287" s="4">
         <v>1</v>
       </c>
-      <c r="E287" s="6" t="inlineStr">
+      <c r="E287" s="4">
+        <v>1</v>
+      </c>
+      <c r="F287" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19162,7 +20026,10 @@
       <c r="D288" s="4">
         <v>1</v>
       </c>
-      <c r="E288" s="6" t="inlineStr">
+      <c r="E288" s="4">
+        <v>1</v>
+      </c>
+      <c r="F288" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19188,9 +20055,12 @@
         </is>
       </c>
       <c r="D289" s="4">
+        <v>2</v>
+      </c>
+      <c r="E289" s="4">
         <v>1</v>
       </c>
-      <c r="E289" s="6" t="inlineStr">
+      <c r="F289" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19261,7 +20131,10 @@
       <c r="D290" s="4">
         <v>2</v>
       </c>
-      <c r="E290" s="6" t="inlineStr">
+      <c r="E290" s="4">
+        <v>2</v>
+      </c>
+      <c r="F290" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19330,9 +20203,12 @@
         </is>
       </c>
       <c r="D291" s="4">
+        <v>2</v>
+      </c>
+      <c r="E291" s="4">
         <v>1</v>
       </c>
-      <c r="E291" s="6" t="inlineStr">
+      <c r="F291" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19403,7 +20279,10 @@
       <c r="D292" s="4">
         <v>1</v>
       </c>
-      <c r="E292" s="6" t="inlineStr">
+      <c r="E292" s="4">
+        <v>1</v>
+      </c>
+      <c r="F292" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19431,7 +20310,10 @@
       <c r="D293" s="4">
         <v>1</v>
       </c>
-      <c r="E293" s="6" t="inlineStr">
+      <c r="E293" s="4">
+        <v>1</v>
+      </c>
+      <c r="F293" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19507,9 +20389,12 @@
         </is>
       </c>
       <c r="D294" s="4">
+        <v>4</v>
+      </c>
+      <c r="E294" s="4">
         <v>1</v>
       </c>
-      <c r="E294" s="6" t="inlineStr">
+      <c r="F294" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19563,9 +20448,12 @@
         </is>
       </c>
       <c r="D295" s="4">
+        <v>4</v>
+      </c>
+      <c r="E295" s="4">
         <v>2</v>
       </c>
-      <c r="E295" s="6" t="inlineStr">
+      <c r="F295" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19619,9 +20507,12 @@
         </is>
       </c>
       <c r="D296" s="4">
+        <v>4</v>
+      </c>
+      <c r="E296" s="4">
         <v>3</v>
       </c>
-      <c r="E296" s="6" t="inlineStr">
+      <c r="F296" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19675,9 +20566,12 @@
         </is>
       </c>
       <c r="D297" s="4">
+        <v>4</v>
+      </c>
+      <c r="E297" s="4">
         <v>1</v>
       </c>
-      <c r="E297" s="6" t="inlineStr">
+      <c r="F297" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19738,9 +20632,12 @@
         </is>
       </c>
       <c r="D298" s="4">
+        <v>4</v>
+      </c>
+      <c r="E298" s="4">
         <v>1</v>
       </c>
-      <c r="E298" s="6" t="inlineStr">
+      <c r="F298" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -19766,9 +20663,12 @@
         </is>
       </c>
       <c r="D299" s="4">
+        <v>7</v>
+      </c>
+      <c r="E299" s="4">
         <v>1</v>
       </c>
-      <c r="E299" s="6" t="inlineStr">
+      <c r="F299" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19837,9 +20737,12 @@
         </is>
       </c>
       <c r="D300" s="4">
+        <v>7</v>
+      </c>
+      <c r="E300" s="4">
         <v>2</v>
       </c>
-      <c r="E300" s="6" t="inlineStr">
+      <c r="F300" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19908,9 +20811,12 @@
         </is>
       </c>
       <c r="D301" s="4">
+        <v>7</v>
+      </c>
+      <c r="E301" s="4">
         <v>3</v>
       </c>
-      <c r="E301" s="6" t="inlineStr">
+      <c r="F301" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -19979,9 +20885,12 @@
         </is>
       </c>
       <c r="D302" s="4">
+        <v>7</v>
+      </c>
+      <c r="E302" s="4">
         <v>4</v>
       </c>
-      <c r="E302" s="6" t="inlineStr">
+      <c r="F302" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20050,9 +20959,12 @@
         </is>
       </c>
       <c r="D303" s="4">
+        <v>5</v>
+      </c>
+      <c r="E303" s="4">
         <v>1</v>
       </c>
-      <c r="E303" s="6" t="inlineStr">
+      <c r="F303" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20121,9 +21033,12 @@
         </is>
       </c>
       <c r="D304" s="4">
+        <v>5</v>
+      </c>
+      <c r="E304" s="4">
         <v>2</v>
       </c>
-      <c r="E304" s="6" t="inlineStr">
+      <c r="F304" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20192,9 +21107,12 @@
         </is>
       </c>
       <c r="D305" s="4">
+        <v>10</v>
+      </c>
+      <c r="E305" s="4">
         <v>1</v>
       </c>
-      <c r="E305" s="6" t="inlineStr">
+      <c r="F305" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20263,9 +21181,12 @@
         </is>
       </c>
       <c r="D306" s="4">
+        <v>10</v>
+      </c>
+      <c r="E306" s="4">
         <v>2</v>
       </c>
-      <c r="E306" s="6" t="inlineStr">
+      <c r="F306" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20334,9 +21255,12 @@
         </is>
       </c>
       <c r="D307" s="4">
+        <v>10</v>
+      </c>
+      <c r="E307" s="4">
         <v>3</v>
       </c>
-      <c r="E307" s="6" t="inlineStr">
+      <c r="F307" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20405,9 +21329,12 @@
         </is>
       </c>
       <c r="D308" s="4">
+        <v>10</v>
+      </c>
+      <c r="E308" s="4">
         <v>4</v>
       </c>
-      <c r="E308" s="6" t="inlineStr">
+      <c r="F308" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20476,9 +21403,12 @@
         </is>
       </c>
       <c r="D309" s="4">
+        <v>10</v>
+      </c>
+      <c r="E309" s="4">
         <v>5</v>
       </c>
-      <c r="E309" s="6" t="inlineStr">
+      <c r="F309" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20547,9 +21477,12 @@
         </is>
       </c>
       <c r="D310" s="4">
+        <v>3</v>
+      </c>
+      <c r="E310" s="4">
         <v>1</v>
       </c>
-      <c r="E310" s="6" t="inlineStr">
+      <c r="F310" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20625,9 +21558,12 @@
         </is>
       </c>
       <c r="D311" s="4">
+        <v>3</v>
+      </c>
+      <c r="E311" s="4">
         <v>2</v>
       </c>
-      <c r="E311" s="6" t="inlineStr">
+      <c r="F311" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20705,7 +21641,10 @@
       <c r="D312" s="4">
         <v>3</v>
       </c>
-      <c r="E312" s="6" t="inlineStr">
+      <c r="E312" s="4">
+        <v>3</v>
+      </c>
+      <c r="F312" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20781,9 +21720,12 @@
         </is>
       </c>
       <c r="D313" s="4">
+        <v>4</v>
+      </c>
+      <c r="E313" s="4">
         <v>1</v>
       </c>
-      <c r="E313" s="6" t="inlineStr">
+      <c r="F313" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20859,9 +21801,12 @@
         </is>
       </c>
       <c r="D314" s="4">
+        <v>4</v>
+      </c>
+      <c r="E314" s="4">
         <v>2</v>
       </c>
-      <c r="E314" s="6" t="inlineStr">
+      <c r="F314" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -20937,9 +21882,12 @@
         </is>
       </c>
       <c r="D315" s="4">
+        <v>2</v>
+      </c>
+      <c r="E315" s="4">
         <v>1</v>
       </c>
-      <c r="E315" s="6" t="inlineStr">
+      <c r="F315" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21015,9 +21963,12 @@
         </is>
       </c>
       <c r="D316" s="4">
+        <v>3</v>
+      </c>
+      <c r="E316" s="4">
         <v>1</v>
       </c>
-      <c r="E316" s="6" t="inlineStr">
+      <c r="F316" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21101,9 +22052,12 @@
         </is>
       </c>
       <c r="D317" s="4">
+        <v>3</v>
+      </c>
+      <c r="E317" s="4">
         <v>1</v>
       </c>
-      <c r="E317" s="6" t="inlineStr">
+      <c r="F317" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21189,7 +22143,10 @@
       <c r="D318" s="4">
         <v>1</v>
       </c>
-      <c r="E318" s="6" t="inlineStr">
+      <c r="E318" s="4">
+        <v>1</v>
+      </c>
+      <c r="F318" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21290,7 +22247,10 @@
       <c r="D319" s="4">
         <v>1</v>
       </c>
-      <c r="E319" s="6" t="inlineStr">
+      <c r="E319" s="4">
+        <v>1</v>
+      </c>
+      <c r="F319" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21391,7 +22351,10 @@
       <c r="D320" s="4">
         <v>1</v>
       </c>
-      <c r="E320" s="6" t="inlineStr">
+      <c r="E320" s="4">
+        <v>1</v>
+      </c>
+      <c r="F320" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -21417,9 +22380,12 @@
         </is>
       </c>
       <c r="D321" s="4">
+        <v>3</v>
+      </c>
+      <c r="E321" s="4">
         <v>1</v>
       </c>
-      <c r="E321" s="6" t="inlineStr">
+      <c r="F321" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21473,9 +22439,12 @@
         </is>
       </c>
       <c r="D322" s="4">
+        <v>3</v>
+      </c>
+      <c r="E322" s="4">
         <v>2</v>
       </c>
-      <c r="E322" s="6" t="inlineStr">
+      <c r="F322" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21531,7 +22500,10 @@
       <c r="D323" s="4">
         <v>3</v>
       </c>
-      <c r="E323" s="6" t="inlineStr">
+      <c r="E323" s="4">
+        <v>3</v>
+      </c>
+      <c r="F323" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21587,7 +22559,10 @@
       <c r="D324" s="4">
         <v>1</v>
       </c>
-      <c r="E324" s="6" t="inlineStr">
+      <c r="E324" s="4">
+        <v>1</v>
+      </c>
+      <c r="F324" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -21613,9 +22588,12 @@
         </is>
       </c>
       <c r="D325" s="4">
+        <v>5</v>
+      </c>
+      <c r="E325" s="4">
         <v>1</v>
       </c>
-      <c r="E325" s="6" t="inlineStr">
+      <c r="F325" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21676,9 +22654,12 @@
         </is>
       </c>
       <c r="D326" s="4">
+        <v>5</v>
+      </c>
+      <c r="E326" s="4">
         <v>2</v>
       </c>
-      <c r="E326" s="6" t="inlineStr">
+      <c r="F326" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21739,9 +22720,12 @@
         </is>
       </c>
       <c r="D327" s="4">
+        <v>5</v>
+      </c>
+      <c r="E327" s="4">
         <v>3</v>
       </c>
-      <c r="E327" s="6" t="inlineStr">
+      <c r="F327" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21802,9 +22786,12 @@
         </is>
       </c>
       <c r="D328" s="4">
+        <v>4</v>
+      </c>
+      <c r="E328" s="4">
         <v>1</v>
       </c>
-      <c r="E328" s="6" t="inlineStr">
+      <c r="F328" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21865,9 +22852,12 @@
         </is>
       </c>
       <c r="D329" s="4">
+        <v>4</v>
+      </c>
+      <c r="E329" s="4">
         <v>1</v>
       </c>
-      <c r="E329" s="6" t="inlineStr">
+      <c r="F329" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21928,9 +22918,12 @@
         </is>
       </c>
       <c r="D330" s="4">
+        <v>4</v>
+      </c>
+      <c r="E330" s="4">
         <v>2</v>
       </c>
-      <c r="E330" s="6" t="inlineStr">
+      <c r="F330" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -21993,7 +22986,10 @@
       <c r="D331" s="4">
         <v>1</v>
       </c>
-      <c r="E331" s="6" t="inlineStr">
+      <c r="E331" s="4">
+        <v>1</v>
+      </c>
+      <c r="F331" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22021,7 +23017,10 @@
       <c r="D332" s="4">
         <v>1</v>
       </c>
-      <c r="E332" s="6" t="inlineStr">
+      <c r="E332" s="4">
+        <v>1</v>
+      </c>
+      <c r="F332" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22047,9 +23046,12 @@
         </is>
       </c>
       <c r="D333" s="4">
+        <v>2</v>
+      </c>
+      <c r="E333" s="4">
         <v>1</v>
       </c>
-      <c r="E333" s="6" t="inlineStr">
+      <c r="F333" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22075,9 +23077,12 @@
         </is>
       </c>
       <c r="D334" s="4">
+        <v>3</v>
+      </c>
+      <c r="E334" s="4">
         <v>1</v>
       </c>
-      <c r="E334" s="6" t="inlineStr">
+      <c r="F334" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22153,9 +23158,12 @@
         </is>
       </c>
       <c r="D335" s="4">
+        <v>3</v>
+      </c>
+      <c r="E335" s="4">
         <v>2</v>
       </c>
-      <c r="E335" s="6" t="inlineStr">
+      <c r="F335" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22231,9 +23239,12 @@
         </is>
       </c>
       <c r="D336" s="4">
+        <v>3</v>
+      </c>
+      <c r="E336" s="4">
         <v>1</v>
       </c>
-      <c r="E336" s="6" t="inlineStr">
+      <c r="F336" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22311,7 +23322,10 @@
       <c r="D337" s="4">
         <v>1</v>
       </c>
-      <c r="E337" s="6" t="inlineStr">
+      <c r="E337" s="4">
+        <v>1</v>
+      </c>
+      <c r="F337" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22337,9 +23351,12 @@
         </is>
       </c>
       <c r="D338" s="4">
+        <v>3</v>
+      </c>
+      <c r="E338" s="4">
         <v>1</v>
       </c>
-      <c r="E338" s="6" t="inlineStr">
+      <c r="F338" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22423,9 +23440,12 @@
         </is>
       </c>
       <c r="D339" s="4">
+        <v>3</v>
+      </c>
+      <c r="E339" s="4">
         <v>2</v>
       </c>
-      <c r="E339" s="6" t="inlineStr">
+      <c r="F339" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22511,7 +23531,10 @@
       <c r="D340" s="4">
         <v>3</v>
       </c>
-      <c r="E340" s="6" t="inlineStr">
+      <c r="E340" s="4">
+        <v>3</v>
+      </c>
+      <c r="F340" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22597,7 +23620,10 @@
       <c r="D341" s="4">
         <v>1</v>
       </c>
-      <c r="E341" s="6" t="inlineStr">
+      <c r="E341" s="4">
+        <v>1</v>
+      </c>
+      <c r="F341" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22625,7 +23651,10 @@
       <c r="D342" s="4">
         <v>1</v>
       </c>
-      <c r="E342" s="6" t="inlineStr">
+      <c r="E342" s="4">
+        <v>1</v>
+      </c>
+      <c r="F342" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22653,7 +23682,10 @@
       <c r="D343" s="4">
         <v>1</v>
       </c>
-      <c r="E343" s="6" t="inlineStr">
+      <c r="E343" s="4">
+        <v>1</v>
+      </c>
+      <c r="F343" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22681,7 +23713,10 @@
       <c r="D344" s="4">
         <v>1</v>
       </c>
-      <c r="E344" s="6" t="inlineStr">
+      <c r="E344" s="4">
+        <v>1</v>
+      </c>
+      <c r="F344" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22707,9 +23742,12 @@
         </is>
       </c>
       <c r="D345" s="4">
+        <v>2</v>
+      </c>
+      <c r="E345" s="4">
         <v>1</v>
       </c>
-      <c r="E345" s="6" t="inlineStr">
+      <c r="F345" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22765,7 +23803,10 @@
       <c r="D346" s="4">
         <v>2</v>
       </c>
-      <c r="E346" s="6" t="inlineStr">
+      <c r="E346" s="4">
+        <v>2</v>
+      </c>
+      <c r="F346" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22819,9 +23860,12 @@
         </is>
       </c>
       <c r="D347" s="4">
+        <v>3</v>
+      </c>
+      <c r="E347" s="4">
         <v>1</v>
       </c>
-      <c r="E347" s="6" t="inlineStr">
+      <c r="F347" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22882,9 +23926,12 @@
         </is>
       </c>
       <c r="D348" s="4">
+        <v>3</v>
+      </c>
+      <c r="E348" s="4">
         <v>2</v>
       </c>
-      <c r="E348" s="6" t="inlineStr">
+      <c r="F348" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -22945,9 +23992,12 @@
         </is>
       </c>
       <c r="D349" s="4">
+        <v>2</v>
+      </c>
+      <c r="E349" s="4">
         <v>1</v>
       </c>
-      <c r="E349" s="6" t="inlineStr">
+      <c r="F349" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -22973,9 +24023,12 @@
         </is>
       </c>
       <c r="D350" s="4">
+        <v>2</v>
+      </c>
+      <c r="E350" s="4">
         <v>1</v>
       </c>
-      <c r="E350" s="6" t="inlineStr">
+      <c r="F350" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -23001,9 +24054,12 @@
         </is>
       </c>
       <c r="D351" s="4">
+        <v>3</v>
+      </c>
+      <c r="E351" s="4">
         <v>1</v>
       </c>
-      <c r="E351" s="6" t="inlineStr">
+      <c r="F351" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23072,9 +24128,12 @@
         </is>
       </c>
       <c r="D352" s="4">
+        <v>3</v>
+      </c>
+      <c r="E352" s="4">
         <v>2</v>
       </c>
-      <c r="E352" s="6" t="inlineStr">
+      <c r="F352" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23143,9 +24202,12 @@
         </is>
       </c>
       <c r="D353" s="4">
+        <v>3</v>
+      </c>
+      <c r="E353" s="4">
         <v>1</v>
       </c>
-      <c r="E353" s="6" t="inlineStr">
+      <c r="F353" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23214,9 +24276,12 @@
         </is>
       </c>
       <c r="D354" s="4">
+        <v>3</v>
+      </c>
+      <c r="E354" s="4">
         <v>2</v>
       </c>
-      <c r="E354" s="6" t="inlineStr">
+      <c r="F354" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23287,7 +24352,10 @@
       <c r="D355" s="4">
         <v>1</v>
       </c>
-      <c r="E355" s="6" t="inlineStr">
+      <c r="E355" s="4">
+        <v>1</v>
+      </c>
+      <c r="F355" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23363,9 +24431,12 @@
         </is>
       </c>
       <c r="D356" s="4">
+        <v>2</v>
+      </c>
+      <c r="E356" s="4">
         <v>1</v>
       </c>
-      <c r="E356" s="6" t="inlineStr">
+      <c r="F356" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23443,7 +24514,10 @@
       <c r="D357" s="4">
         <v>1</v>
       </c>
-      <c r="E357" s="6" t="inlineStr">
+      <c r="E357" s="4">
+        <v>1</v>
+      </c>
+      <c r="F357" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -23471,7 +24545,10 @@
       <c r="D358" s="4">
         <v>1</v>
       </c>
-      <c r="E358" s="6" t="inlineStr">
+      <c r="E358" s="4">
+        <v>1</v>
+      </c>
+      <c r="F358" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23564,7 +24641,10 @@
       <c r="D359" s="4">
         <v>1</v>
       </c>
-      <c r="E359" s="6" t="inlineStr">
+      <c r="E359" s="4">
+        <v>1</v>
+      </c>
+      <c r="F359" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23657,7 +24737,10 @@
       <c r="D360" s="4">
         <v>1</v>
       </c>
-      <c r="E360" s="6" t="inlineStr">
+      <c r="E360" s="4">
+        <v>1</v>
+      </c>
+      <c r="F360" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -23683,9 +24766,12 @@
         </is>
       </c>
       <c r="D361" s="4">
+        <v>6</v>
+      </c>
+      <c r="E361" s="4">
         <v>1</v>
       </c>
-      <c r="E361" s="6" t="inlineStr">
+      <c r="F361" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23739,9 +24825,12 @@
         </is>
       </c>
       <c r="D362" s="4">
+        <v>6</v>
+      </c>
+      <c r="E362" s="4">
         <v>2</v>
       </c>
-      <c r="E362" s="6" t="inlineStr">
+      <c r="F362" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23795,9 +24884,12 @@
         </is>
       </c>
       <c r="D363" s="4">
+        <v>6</v>
+      </c>
+      <c r="E363" s="4">
         <v>3</v>
       </c>
-      <c r="E363" s="6" t="inlineStr">
+      <c r="F363" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23851,9 +24943,12 @@
         </is>
       </c>
       <c r="D364" s="4">
+        <v>6</v>
+      </c>
+      <c r="E364" s="4">
         <v>4</v>
       </c>
-      <c r="E364" s="6" t="inlineStr">
+      <c r="F364" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23907,9 +25002,12 @@
         </is>
       </c>
       <c r="D365" s="4">
+        <v>6</v>
+      </c>
+      <c r="E365" s="4">
         <v>5</v>
       </c>
-      <c r="E365" s="6" t="inlineStr">
+      <c r="F365" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -23965,7 +25063,10 @@
       <c r="D366" s="4">
         <v>6</v>
       </c>
-      <c r="E366" s="6" t="inlineStr">
+      <c r="E366" s="4">
+        <v>6</v>
+      </c>
+      <c r="F366" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24019,9 +25120,12 @@
         </is>
       </c>
       <c r="D367" s="4">
+        <v>2</v>
+      </c>
+      <c r="E367" s="4">
         <v>1</v>
       </c>
-      <c r="E367" s="6" t="inlineStr">
+      <c r="F367" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24077,7 +25181,10 @@
       <c r="D368" s="4">
         <v>2</v>
       </c>
-      <c r="E368" s="6" t="inlineStr">
+      <c r="E368" s="4">
+        <v>2</v>
+      </c>
+      <c r="F368" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24131,9 +25238,12 @@
         </is>
       </c>
       <c r="D369" s="4">
+        <v>2</v>
+      </c>
+      <c r="E369" s="4">
         <v>1</v>
       </c>
-      <c r="E369" s="6" t="inlineStr">
+      <c r="F369" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24189,7 +25299,10 @@
       <c r="D370" s="4">
         <v>2</v>
       </c>
-      <c r="E370" s="6" t="inlineStr">
+      <c r="E370" s="4">
+        <v>2</v>
+      </c>
+      <c r="F370" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24245,7 +25358,10 @@
       <c r="D371" s="4">
         <v>1</v>
       </c>
-      <c r="E371" s="6" t="inlineStr">
+      <c r="E371" s="4">
+        <v>1</v>
+      </c>
+      <c r="F371" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24299,9 +25415,12 @@
         </is>
       </c>
       <c r="D372" s="4">
+        <v>3</v>
+      </c>
+      <c r="E372" s="4">
         <v>1</v>
       </c>
-      <c r="E372" s="6" t="inlineStr">
+      <c r="F372" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24355,9 +25474,12 @@
         </is>
       </c>
       <c r="D373" s="4">
+        <v>3</v>
+      </c>
+      <c r="E373" s="4">
         <v>2</v>
       </c>
-      <c r="E373" s="6" t="inlineStr">
+      <c r="F373" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24413,7 +25535,10 @@
       <c r="D374" s="4">
         <v>3</v>
       </c>
-      <c r="E374" s="6" t="inlineStr">
+      <c r="E374" s="4">
+        <v>3</v>
+      </c>
+      <c r="F374" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24469,7 +25594,10 @@
       <c r="D375" s="4">
         <v>1</v>
       </c>
-      <c r="E375" s="6" t="inlineStr">
+      <c r="E375" s="4">
+        <v>1</v>
+      </c>
+      <c r="F375" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24525,7 +25653,10 @@
       <c r="D376" s="4">
         <v>1</v>
       </c>
-      <c r="E376" s="6" t="inlineStr">
+      <c r="E376" s="4">
+        <v>1</v>
+      </c>
+      <c r="F376" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24579,9 +25710,12 @@
         </is>
       </c>
       <c r="D377" s="4">
+        <v>7</v>
+      </c>
+      <c r="E377" s="4">
         <v>1</v>
       </c>
-      <c r="E377" s="6" t="inlineStr">
+      <c r="F377" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24635,9 +25769,12 @@
         </is>
       </c>
       <c r="D378" s="4">
+        <v>7</v>
+      </c>
+      <c r="E378" s="4">
         <v>2</v>
       </c>
-      <c r="E378" s="6" t="inlineStr">
+      <c r="F378" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24691,9 +25828,12 @@
         </is>
       </c>
       <c r="D379" s="4">
+        <v>7</v>
+      </c>
+      <c r="E379" s="4">
         <v>3</v>
       </c>
-      <c r="E379" s="6" t="inlineStr">
+      <c r="F379" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24747,9 +25887,12 @@
         </is>
       </c>
       <c r="D380" s="4">
+        <v>7</v>
+      </c>
+      <c r="E380" s="4">
         <v>4</v>
       </c>
-      <c r="E380" s="6" t="inlineStr">
+      <c r="F380" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24803,9 +25946,12 @@
         </is>
       </c>
       <c r="D381" s="4">
+        <v>7</v>
+      </c>
+      <c r="E381" s="4">
         <v>5</v>
       </c>
-      <c r="E381" s="6" t="inlineStr">
+      <c r="F381" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24859,9 +26005,12 @@
         </is>
       </c>
       <c r="D382" s="4">
+        <v>7</v>
+      </c>
+      <c r="E382" s="4">
         <v>6</v>
       </c>
-      <c r="E382" s="6" t="inlineStr">
+      <c r="F382" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24917,7 +26066,10 @@
       <c r="D383" s="4">
         <v>7</v>
       </c>
-      <c r="E383" s="6" t="inlineStr">
+      <c r="E383" s="4">
+        <v>7</v>
+      </c>
+      <c r="F383" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -24971,9 +26123,12 @@
         </is>
       </c>
       <c r="D384" s="4">
+        <v>28</v>
+      </c>
+      <c r="E384" s="4">
         <v>1</v>
       </c>
-      <c r="E384" s="6" t="inlineStr">
+      <c r="F384" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25027,9 +26182,12 @@
         </is>
       </c>
       <c r="D385" s="4">
+        <v>28</v>
+      </c>
+      <c r="E385" s="4">
         <v>2</v>
       </c>
-      <c r="E385" s="6" t="inlineStr">
+      <c r="F385" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25083,9 +26241,12 @@
         </is>
       </c>
       <c r="D386" s="4">
+        <v>28</v>
+      </c>
+      <c r="E386" s="4">
         <v>3</v>
       </c>
-      <c r="E386" s="6" t="inlineStr">
+      <c r="F386" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25139,9 +26300,12 @@
         </is>
       </c>
       <c r="D387" s="4">
+        <v>28</v>
+      </c>
+      <c r="E387" s="4">
         <v>4</v>
       </c>
-      <c r="E387" s="6" t="inlineStr">
+      <c r="F387" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25195,9 +26359,12 @@
         </is>
       </c>
       <c r="D388" s="4">
+        <v>28</v>
+      </c>
+      <c r="E388" s="4">
         <v>5</v>
       </c>
-      <c r="E388" s="6" t="inlineStr">
+      <c r="F388" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25251,9 +26418,12 @@
         </is>
       </c>
       <c r="D389" s="4">
+        <v>28</v>
+      </c>
+      <c r="E389" s="4">
         <v>6</v>
       </c>
-      <c r="E389" s="6" t="inlineStr">
+      <c r="F389" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25307,9 +26477,12 @@
         </is>
       </c>
       <c r="D390" s="4">
+        <v>28</v>
+      </c>
+      <c r="E390" s="4">
         <v>7</v>
       </c>
-      <c r="E390" s="6" t="inlineStr">
+      <c r="F390" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25363,9 +26536,12 @@
         </is>
       </c>
       <c r="D391" s="4">
+        <v>28</v>
+      </c>
+      <c r="E391" s="4">
         <v>8</v>
       </c>
-      <c r="E391" s="6" t="inlineStr">
+      <c r="F391" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25419,9 +26595,12 @@
         </is>
       </c>
       <c r="D392" s="4">
+        <v>28</v>
+      </c>
+      <c r="E392" s="4">
         <v>9</v>
       </c>
-      <c r="E392" s="6" t="inlineStr">
+      <c r="F392" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25475,9 +26654,12 @@
         </is>
       </c>
       <c r="D393" s="4">
+        <v>28</v>
+      </c>
+      <c r="E393" s="4">
         <v>10</v>
       </c>
-      <c r="E393" s="6" t="inlineStr">
+      <c r="F393" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25531,9 +26713,12 @@
         </is>
       </c>
       <c r="D394" s="4">
+        <v>28</v>
+      </c>
+      <c r="E394" s="4">
         <v>11</v>
       </c>
-      <c r="E394" s="6" t="inlineStr">
+      <c r="F394" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25587,9 +26772,12 @@
         </is>
       </c>
       <c r="D395" s="4">
+        <v>28</v>
+      </c>
+      <c r="E395" s="4">
         <v>12</v>
       </c>
-      <c r="E395" s="6" t="inlineStr">
+      <c r="F395" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25643,9 +26831,12 @@
         </is>
       </c>
       <c r="D396" s="4">
+        <v>28</v>
+      </c>
+      <c r="E396" s="4">
         <v>13</v>
       </c>
-      <c r="E396" s="6" t="inlineStr">
+      <c r="F396" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25699,9 +26890,12 @@
         </is>
       </c>
       <c r="D397" s="4">
+        <v>28</v>
+      </c>
+      <c r="E397" s="4">
         <v>14</v>
       </c>
-      <c r="E397" s="6" t="inlineStr">
+      <c r="F397" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25755,9 +26949,12 @@
         </is>
       </c>
       <c r="D398" s="4">
+        <v>28</v>
+      </c>
+      <c r="E398" s="4">
         <v>15</v>
       </c>
-      <c r="E398" s="6" t="inlineStr">
+      <c r="F398" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25811,9 +27008,12 @@
         </is>
       </c>
       <c r="D399" s="4">
+        <v>28</v>
+      </c>
+      <c r="E399" s="4">
         <v>16</v>
       </c>
-      <c r="E399" s="6" t="inlineStr">
+      <c r="F399" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25867,9 +27067,12 @@
         </is>
       </c>
       <c r="D400" s="4">
+        <v>28</v>
+      </c>
+      <c r="E400" s="4">
         <v>17</v>
       </c>
-      <c r="E400" s="6" t="inlineStr">
+      <c r="F400" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25923,9 +27126,12 @@
         </is>
       </c>
       <c r="D401" s="4">
+        <v>28</v>
+      </c>
+      <c r="E401" s="4">
         <v>18</v>
       </c>
-      <c r="E401" s="6" t="inlineStr">
+      <c r="F401" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -25979,9 +27185,12 @@
         </is>
       </c>
       <c r="D402" s="4">
+        <v>28</v>
+      </c>
+      <c r="E402" s="4">
         <v>19</v>
       </c>
-      <c r="E402" s="6" t="inlineStr">
+      <c r="F402" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26035,9 +27244,12 @@
         </is>
       </c>
       <c r="D403" s="4">
+        <v>28</v>
+      </c>
+      <c r="E403" s="4">
         <v>20</v>
       </c>
-      <c r="E403" s="6" t="inlineStr">
+      <c r="F403" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26091,9 +27303,12 @@
         </is>
       </c>
       <c r="D404" s="4">
+        <v>6</v>
+      </c>
+      <c r="E404" s="4">
         <v>1</v>
       </c>
-      <c r="E404" s="6" t="inlineStr">
+      <c r="F404" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26147,9 +27362,12 @@
         </is>
       </c>
       <c r="D405" s="4">
+        <v>6</v>
+      </c>
+      <c r="E405" s="4">
         <v>2</v>
       </c>
-      <c r="E405" s="6" t="inlineStr">
+      <c r="F405" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26203,9 +27421,12 @@
         </is>
       </c>
       <c r="D406" s="4">
+        <v>6</v>
+      </c>
+      <c r="E406" s="4">
         <v>3</v>
       </c>
-      <c r="E406" s="6" t="inlineStr">
+      <c r="F406" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26259,9 +27480,12 @@
         </is>
       </c>
       <c r="D407" s="4">
+        <v>6</v>
+      </c>
+      <c r="E407" s="4">
         <v>4</v>
       </c>
-      <c r="E407" s="6" t="inlineStr">
+      <c r="F407" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26315,9 +27539,12 @@
         </is>
       </c>
       <c r="D408" s="4">
+        <v>6</v>
+      </c>
+      <c r="E408" s="4">
         <v>5</v>
       </c>
-      <c r="E408" s="6" t="inlineStr">
+      <c r="F408" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26373,7 +27600,10 @@
       <c r="D409" s="4">
         <v>6</v>
       </c>
-      <c r="E409" s="6" t="inlineStr">
+      <c r="E409" s="4">
+        <v>6</v>
+      </c>
+      <c r="F409" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26427,9 +27657,12 @@
         </is>
       </c>
       <c r="D410" s="4">
+        <v>3</v>
+      </c>
+      <c r="E410" s="4">
         <v>1</v>
       </c>
-      <c r="E410" s="6" t="inlineStr">
+      <c r="F410" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26483,9 +27716,12 @@
         </is>
       </c>
       <c r="D411" s="4">
+        <v>3</v>
+      </c>
+      <c r="E411" s="4">
         <v>2</v>
       </c>
-      <c r="E411" s="6" t="inlineStr">
+      <c r="F411" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26541,7 +27777,10 @@
       <c r="D412" s="4">
         <v>3</v>
       </c>
-      <c r="E412" s="6" t="inlineStr">
+      <c r="E412" s="4">
+        <v>3</v>
+      </c>
+      <c r="F412" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26595,9 +27834,12 @@
         </is>
       </c>
       <c r="D413" s="4">
+        <v>8</v>
+      </c>
+      <c r="E413" s="4">
         <v>1</v>
       </c>
-      <c r="E413" s="6" t="inlineStr">
+      <c r="F413" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26651,9 +27893,12 @@
         </is>
       </c>
       <c r="D414" s="4">
+        <v>8</v>
+      </c>
+      <c r="E414" s="4">
         <v>2</v>
       </c>
-      <c r="E414" s="6" t="inlineStr">
+      <c r="F414" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26707,9 +27952,12 @@
         </is>
       </c>
       <c r="D415" s="4">
+        <v>8</v>
+      </c>
+      <c r="E415" s="4">
         <v>3</v>
       </c>
-      <c r="E415" s="6" t="inlineStr">
+      <c r="F415" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26763,9 +28011,12 @@
         </is>
       </c>
       <c r="D416" s="4">
+        <v>8</v>
+      </c>
+      <c r="E416" s="4">
         <v>4</v>
       </c>
-      <c r="E416" s="6" t="inlineStr">
+      <c r="F416" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26819,9 +28070,12 @@
         </is>
       </c>
       <c r="D417" s="4">
+        <v>8</v>
+      </c>
+      <c r="E417" s="4">
         <v>5</v>
       </c>
-      <c r="E417" s="6" t="inlineStr">
+      <c r="F417" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26875,9 +28129,12 @@
         </is>
       </c>
       <c r="D418" s="4">
+        <v>8</v>
+      </c>
+      <c r="E418" s="4">
         <v>6</v>
       </c>
-      <c r="E418" s="6" t="inlineStr">
+      <c r="F418" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26931,9 +28188,12 @@
         </is>
       </c>
       <c r="D419" s="4">
+        <v>8</v>
+      </c>
+      <c r="E419" s="4">
         <v>7</v>
       </c>
-      <c r="E419" s="6" t="inlineStr">
+      <c r="F419" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -26987,9 +28247,12 @@
         </is>
       </c>
       <c r="D420" s="4">
+        <v>2</v>
+      </c>
+      <c r="E420" s="4">
         <v>1</v>
       </c>
-      <c r="E420" s="6" t="inlineStr">
+      <c r="F420" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27045,7 +28308,10 @@
       <c r="D421" s="4">
         <v>2</v>
       </c>
-      <c r="E421" s="6" t="inlineStr">
+      <c r="E421" s="4">
+        <v>2</v>
+      </c>
+      <c r="F421" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27099,9 +28365,12 @@
         </is>
       </c>
       <c r="D422" s="4">
+        <v>2</v>
+      </c>
+      <c r="E422" s="4">
         <v>1</v>
       </c>
-      <c r="E422" s="6" t="inlineStr">
+      <c r="F422" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27157,7 +28426,10 @@
       <c r="D423" s="4">
         <v>2</v>
       </c>
-      <c r="E423" s="6" t="inlineStr">
+      <c r="E423" s="4">
+        <v>2</v>
+      </c>
+      <c r="F423" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27211,9 +28483,12 @@
         </is>
       </c>
       <c r="D424" s="4">
+        <v>2</v>
+      </c>
+      <c r="E424" s="4">
         <v>1</v>
       </c>
-      <c r="E424" s="6" t="inlineStr">
+      <c r="F424" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27269,7 +28544,10 @@
       <c r="D425" s="4">
         <v>2</v>
       </c>
-      <c r="E425" s="6" t="inlineStr">
+      <c r="E425" s="4">
+        <v>2</v>
+      </c>
+      <c r="F425" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27323,9 +28601,12 @@
         </is>
       </c>
       <c r="D426" s="4">
+        <v>3</v>
+      </c>
+      <c r="E426" s="4">
         <v>1</v>
       </c>
-      <c r="E426" s="6" t="inlineStr">
+      <c r="F426" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27379,9 +28660,12 @@
         </is>
       </c>
       <c r="D427" s="4">
+        <v>3</v>
+      </c>
+      <c r="E427" s="4">
         <v>2</v>
       </c>
-      <c r="E427" s="6" t="inlineStr">
+      <c r="F427" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27437,7 +28721,10 @@
       <c r="D428" s="4">
         <v>3</v>
       </c>
-      <c r="E428" s="6" t="inlineStr">
+      <c r="E428" s="4">
+        <v>3</v>
+      </c>
+      <c r="F428" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27491,9 +28778,12 @@
         </is>
       </c>
       <c r="D429" s="4">
+        <v>14</v>
+      </c>
+      <c r="E429" s="4">
         <v>1</v>
       </c>
-      <c r="E429" s="6" t="inlineStr">
+      <c r="F429" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27547,9 +28837,12 @@
         </is>
       </c>
       <c r="D430" s="4">
+        <v>14</v>
+      </c>
+      <c r="E430" s="4">
         <v>2</v>
       </c>
-      <c r="E430" s="6" t="inlineStr">
+      <c r="F430" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27603,9 +28896,12 @@
         </is>
       </c>
       <c r="D431" s="4">
+        <v>14</v>
+      </c>
+      <c r="E431" s="4">
         <v>3</v>
       </c>
-      <c r="E431" s="6" t="inlineStr">
+      <c r="F431" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27659,9 +28955,12 @@
         </is>
       </c>
       <c r="D432" s="4">
+        <v>14</v>
+      </c>
+      <c r="E432" s="4">
         <v>4</v>
       </c>
-      <c r="E432" s="6" t="inlineStr">
+      <c r="F432" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27715,9 +29014,12 @@
         </is>
       </c>
       <c r="D433" s="4">
+        <v>14</v>
+      </c>
+      <c r="E433" s="4">
         <v>5</v>
       </c>
-      <c r="E433" s="6" t="inlineStr">
+      <c r="F433" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27771,9 +29073,12 @@
         </is>
       </c>
       <c r="D434" s="4">
+        <v>14</v>
+      </c>
+      <c r="E434" s="4">
         <v>6</v>
       </c>
-      <c r="E434" s="6" t="inlineStr">
+      <c r="F434" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27827,9 +29132,12 @@
         </is>
       </c>
       <c r="D435" s="4">
+        <v>14</v>
+      </c>
+      <c r="E435" s="4">
         <v>7</v>
       </c>
-      <c r="E435" s="6" t="inlineStr">
+      <c r="F435" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27883,9 +29191,12 @@
         </is>
       </c>
       <c r="D436" s="4">
+        <v>14</v>
+      </c>
+      <c r="E436" s="4">
         <v>8</v>
       </c>
-      <c r="E436" s="6" t="inlineStr">
+      <c r="F436" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27939,9 +29250,12 @@
         </is>
       </c>
       <c r="D437" s="4">
+        <v>14</v>
+      </c>
+      <c r="E437" s="4">
         <v>9</v>
       </c>
-      <c r="E437" s="6" t="inlineStr">
+      <c r="F437" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -27995,9 +29309,12 @@
         </is>
       </c>
       <c r="D438" s="4">
+        <v>14</v>
+      </c>
+      <c r="E438" s="4">
         <v>10</v>
       </c>
-      <c r="E438" s="6" t="inlineStr">
+      <c r="F438" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28051,9 +29368,12 @@
         </is>
       </c>
       <c r="D439" s="4">
+        <v>14</v>
+      </c>
+      <c r="E439" s="4">
         <v>11</v>
       </c>
-      <c r="E439" s="6" t="inlineStr">
+      <c r="F439" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28107,9 +29427,12 @@
         </is>
       </c>
       <c r="D440" s="4">
+        <v>14</v>
+      </c>
+      <c r="E440" s="4">
         <v>12</v>
       </c>
-      <c r="E440" s="6" t="inlineStr">
+      <c r="F440" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28163,9 +29486,12 @@
         </is>
       </c>
       <c r="D441" s="4">
+        <v>14</v>
+      </c>
+      <c r="E441" s="4">
         <v>13</v>
       </c>
-      <c r="E441" s="6" t="inlineStr">
+      <c r="F441" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28221,7 +29547,10 @@
       <c r="D442" s="4">
         <v>14</v>
       </c>
-      <c r="E442" s="6" t="inlineStr">
+      <c r="E442" s="4">
+        <v>14</v>
+      </c>
+      <c r="F442" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28275,9 +29604,12 @@
         </is>
       </c>
       <c r="D443" s="4">
+        <v>5</v>
+      </c>
+      <c r="E443" s="4">
         <v>1</v>
       </c>
-      <c r="E443" s="6" t="inlineStr">
+      <c r="F443" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28347,9 +29679,12 @@
         </is>
       </c>
       <c r="D444" s="4">
+        <v>5</v>
+      </c>
+      <c r="E444" s="4">
         <v>2</v>
       </c>
-      <c r="E444" s="6" t="inlineStr">
+      <c r="F444" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28419,9 +29754,12 @@
         </is>
       </c>
       <c r="D445" s="4">
+        <v>5</v>
+      </c>
+      <c r="E445" s="4">
         <v>3</v>
       </c>
-      <c r="E445" s="6" t="inlineStr">
+      <c r="F445" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28491,9 +29829,12 @@
         </is>
       </c>
       <c r="D446" s="4">
+        <v>5</v>
+      </c>
+      <c r="E446" s="4">
         <v>4</v>
       </c>
-      <c r="E446" s="6" t="inlineStr">
+      <c r="F446" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28565,7 +29906,10 @@
       <c r="D447" s="4">
         <v>5</v>
       </c>
-      <c r="E447" s="6" t="inlineStr">
+      <c r="E447" s="4">
+        <v>5</v>
+      </c>
+      <c r="F447" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28635,9 +29979,12 @@
         </is>
       </c>
       <c r="D448" s="4">
+        <v>3</v>
+      </c>
+      <c r="E448" s="4">
         <v>1</v>
       </c>
-      <c r="E448" s="6" t="inlineStr">
+      <c r="F448" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28698,9 +30045,12 @@
         </is>
       </c>
       <c r="D449" s="4">
+        <v>3</v>
+      </c>
+      <c r="E449" s="4">
         <v>2</v>
       </c>
-      <c r="E449" s="6" t="inlineStr">
+      <c r="F449" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28763,7 +30113,10 @@
       <c r="D450" s="4">
         <v>3</v>
       </c>
-      <c r="E450" s="6" t="inlineStr">
+      <c r="E450" s="4">
+        <v>3</v>
+      </c>
+      <c r="F450" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28826,7 +30179,10 @@
       <c r="D451" s="4">
         <v>1</v>
       </c>
-      <c r="E451" s="6" t="inlineStr">
+      <c r="E451" s="4">
+        <v>1</v>
+      </c>
+      <c r="F451" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28887,9 +30243,12 @@
         </is>
       </c>
       <c r="D452" s="4">
+        <v>58</v>
+      </c>
+      <c r="E452" s="4">
         <v>1</v>
       </c>
-      <c r="E452" s="6" t="inlineStr">
+      <c r="F452" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -28950,9 +30309,12 @@
         </is>
       </c>
       <c r="D453" s="4">
+        <v>58</v>
+      </c>
+      <c r="E453" s="4">
         <v>2</v>
       </c>
-      <c r="E453" s="6" t="inlineStr">
+      <c r="F453" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29013,9 +30375,12 @@
         </is>
       </c>
       <c r="D454" s="4">
+        <v>58</v>
+      </c>
+      <c r="E454" s="4">
         <v>3</v>
       </c>
-      <c r="E454" s="6" t="inlineStr">
+      <c r="F454" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29076,9 +30441,12 @@
         </is>
       </c>
       <c r="D455" s="4">
+        <v>58</v>
+      </c>
+      <c r="E455" s="4">
         <v>4</v>
       </c>
-      <c r="E455" s="6" t="inlineStr">
+      <c r="F455" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29139,9 +30507,12 @@
         </is>
       </c>
       <c r="D456" s="4">
+        <v>58</v>
+      </c>
+      <c r="E456" s="4">
         <v>5</v>
       </c>
-      <c r="E456" s="6" t="inlineStr">
+      <c r="F456" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29202,9 +30573,12 @@
         </is>
       </c>
       <c r="D457" s="4">
+        <v>58</v>
+      </c>
+      <c r="E457" s="4">
         <v>6</v>
       </c>
-      <c r="E457" s="6" t="inlineStr">
+      <c r="F457" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29265,9 +30639,12 @@
         </is>
       </c>
       <c r="D458" s="4">
+        <v>58</v>
+      </c>
+      <c r="E458" s="4">
         <v>7</v>
       </c>
-      <c r="E458" s="6" t="inlineStr">
+      <c r="F458" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29328,9 +30705,12 @@
         </is>
       </c>
       <c r="D459" s="4">
+        <v>58</v>
+      </c>
+      <c r="E459" s="4">
         <v>8</v>
       </c>
-      <c r="E459" s="6" t="inlineStr">
+      <c r="F459" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29391,9 +30771,12 @@
         </is>
       </c>
       <c r="D460" s="4">
+        <v>58</v>
+      </c>
+      <c r="E460" s="4">
         <v>9</v>
       </c>
-      <c r="E460" s="6" t="inlineStr">
+      <c r="F460" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29454,9 +30837,12 @@
         </is>
       </c>
       <c r="D461" s="4">
+        <v>58</v>
+      </c>
+      <c r="E461" s="4">
         <v>10</v>
       </c>
-      <c r="E461" s="6" t="inlineStr">
+      <c r="F461" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29517,9 +30903,12 @@
         </is>
       </c>
       <c r="D462" s="4">
+        <v>58</v>
+      </c>
+      <c r="E462" s="4">
         <v>11</v>
       </c>
-      <c r="E462" s="6" t="inlineStr">
+      <c r="F462" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29580,9 +30969,12 @@
         </is>
       </c>
       <c r="D463" s="4">
+        <v>58</v>
+      </c>
+      <c r="E463" s="4">
         <v>12</v>
       </c>
-      <c r="E463" s="6" t="inlineStr">
+      <c r="F463" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29643,9 +31035,12 @@
         </is>
       </c>
       <c r="D464" s="4">
+        <v>58</v>
+      </c>
+      <c r="E464" s="4">
         <v>13</v>
       </c>
-      <c r="E464" s="6" t="inlineStr">
+      <c r="F464" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29706,9 +31101,12 @@
         </is>
       </c>
       <c r="D465" s="4">
+        <v>58</v>
+      </c>
+      <c r="E465" s="4">
         <v>14</v>
       </c>
-      <c r="E465" s="6" t="inlineStr">
+      <c r="F465" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29769,9 +31167,12 @@
         </is>
       </c>
       <c r="D466" s="4">
+        <v>58</v>
+      </c>
+      <c r="E466" s="4">
         <v>15</v>
       </c>
-      <c r="E466" s="6" t="inlineStr">
+      <c r="F466" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29832,9 +31233,12 @@
         </is>
       </c>
       <c r="D467" s="4">
+        <v>58</v>
+      </c>
+      <c r="E467" s="4">
         <v>16</v>
       </c>
-      <c r="E467" s="6" t="inlineStr">
+      <c r="F467" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29895,9 +31299,12 @@
         </is>
       </c>
       <c r="D468" s="4">
+        <v>58</v>
+      </c>
+      <c r="E468" s="4">
         <v>17</v>
       </c>
-      <c r="E468" s="6" t="inlineStr">
+      <c r="F468" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -29958,9 +31365,12 @@
         </is>
       </c>
       <c r="D469" s="4">
+        <v>58</v>
+      </c>
+      <c r="E469" s="4">
         <v>18</v>
       </c>
-      <c r="E469" s="6" t="inlineStr">
+      <c r="F469" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30021,9 +31431,12 @@
         </is>
       </c>
       <c r="D470" s="4">
+        <v>58</v>
+      </c>
+      <c r="E470" s="4">
         <v>19</v>
       </c>
-      <c r="E470" s="6" t="inlineStr">
+      <c r="F470" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30084,9 +31497,12 @@
         </is>
       </c>
       <c r="D471" s="4">
+        <v>58</v>
+      </c>
+      <c r="E471" s="4">
         <v>20</v>
       </c>
-      <c r="E471" s="6" t="inlineStr">
+      <c r="F471" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30147,9 +31563,12 @@
         </is>
       </c>
       <c r="D472" s="4">
+        <v>27</v>
+      </c>
+      <c r="E472" s="4">
         <v>1</v>
       </c>
-      <c r="E472" s="6" t="inlineStr">
+      <c r="F472" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30218,9 +31637,12 @@
         </is>
       </c>
       <c r="D473" s="4">
+        <v>27</v>
+      </c>
+      <c r="E473" s="4">
         <v>2</v>
       </c>
-      <c r="E473" s="6" t="inlineStr">
+      <c r="F473" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30289,9 +31711,12 @@
         </is>
       </c>
       <c r="D474" s="4">
+        <v>27</v>
+      </c>
+      <c r="E474" s="4">
         <v>3</v>
       </c>
-      <c r="E474" s="6" t="inlineStr">
+      <c r="F474" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30360,9 +31785,12 @@
         </is>
       </c>
       <c r="D475" s="4">
+        <v>27</v>
+      </c>
+      <c r="E475" s="4">
         <v>4</v>
       </c>
-      <c r="E475" s="6" t="inlineStr">
+      <c r="F475" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30431,9 +31859,12 @@
         </is>
       </c>
       <c r="D476" s="4">
+        <v>27</v>
+      </c>
+      <c r="E476" s="4">
         <v>5</v>
       </c>
-      <c r="E476" s="6" t="inlineStr">
+      <c r="F476" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30502,9 +31933,12 @@
         </is>
       </c>
       <c r="D477" s="4">
+        <v>27</v>
+      </c>
+      <c r="E477" s="4">
         <v>6</v>
       </c>
-      <c r="E477" s="6" t="inlineStr">
+      <c r="F477" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30573,9 +32007,12 @@
         </is>
       </c>
       <c r="D478" s="4">
+        <v>27</v>
+      </c>
+      <c r="E478" s="4">
         <v>7</v>
       </c>
-      <c r="E478" s="6" t="inlineStr">
+      <c r="F478" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30644,9 +32081,12 @@
         </is>
       </c>
       <c r="D479" s="4">
+        <v>27</v>
+      </c>
+      <c r="E479" s="4">
         <v>8</v>
       </c>
-      <c r="E479" s="6" t="inlineStr">
+      <c r="F479" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30715,9 +32155,12 @@
         </is>
       </c>
       <c r="D480" s="4">
+        <v>27</v>
+      </c>
+      <c r="E480" s="4">
         <v>9</v>
       </c>
-      <c r="E480" s="6" t="inlineStr">
+      <c r="F480" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30786,9 +32229,12 @@
         </is>
       </c>
       <c r="D481" s="4">
+        <v>27</v>
+      </c>
+      <c r="E481" s="4">
         <v>10</v>
       </c>
-      <c r="E481" s="6" t="inlineStr">
+      <c r="F481" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30857,9 +32303,12 @@
         </is>
       </c>
       <c r="D482" s="4">
+        <v>27</v>
+      </c>
+      <c r="E482" s="4">
         <v>11</v>
       </c>
-      <c r="E482" s="6" t="inlineStr">
+      <c r="F482" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30928,9 +32377,12 @@
         </is>
       </c>
       <c r="D483" s="4">
+        <v>27</v>
+      </c>
+      <c r="E483" s="4">
         <v>12</v>
       </c>
-      <c r="E483" s="6" t="inlineStr">
+      <c r="F483" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -30999,9 +32451,12 @@
         </is>
       </c>
       <c r="D484" s="4">
+        <v>27</v>
+      </c>
+      <c r="E484" s="4">
         <v>13</v>
       </c>
-      <c r="E484" s="6" t="inlineStr">
+      <c r="F484" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31070,9 +32525,12 @@
         </is>
       </c>
       <c r="D485" s="4">
+        <v>27</v>
+      </c>
+      <c r="E485" s="4">
         <v>14</v>
       </c>
-      <c r="E485" s="6" t="inlineStr">
+      <c r="F485" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31141,9 +32599,12 @@
         </is>
       </c>
       <c r="D486" s="4">
+        <v>27</v>
+      </c>
+      <c r="E486" s="4">
         <v>15</v>
       </c>
-      <c r="E486" s="6" t="inlineStr">
+      <c r="F486" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31212,9 +32673,12 @@
         </is>
       </c>
       <c r="D487" s="4">
+        <v>27</v>
+      </c>
+      <c r="E487" s="4">
         <v>16</v>
       </c>
-      <c r="E487" s="6" t="inlineStr">
+      <c r="F487" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31283,9 +32747,12 @@
         </is>
       </c>
       <c r="D488" s="4">
+        <v>27</v>
+      </c>
+      <c r="E488" s="4">
         <v>17</v>
       </c>
-      <c r="E488" s="6" t="inlineStr">
+      <c r="F488" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31354,9 +32821,12 @@
         </is>
       </c>
       <c r="D489" s="4">
+        <v>27</v>
+      </c>
+      <c r="E489" s="4">
         <v>18</v>
       </c>
-      <c r="E489" s="6" t="inlineStr">
+      <c r="F489" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31425,9 +32895,12 @@
         </is>
       </c>
       <c r="D490" s="4">
+        <v>27</v>
+      </c>
+      <c r="E490" s="4">
         <v>19</v>
       </c>
-      <c r="E490" s="6" t="inlineStr">
+      <c r="F490" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31496,9 +32969,12 @@
         </is>
       </c>
       <c r="D491" s="4">
+        <v>27</v>
+      </c>
+      <c r="E491" s="4">
         <v>20</v>
       </c>
-      <c r="E491" s="6" t="inlineStr">
+      <c r="F491" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31567,9 +33043,12 @@
         </is>
       </c>
       <c r="D492" s="4">
+        <v>10</v>
+      </c>
+      <c r="E492" s="4">
         <v>1</v>
       </c>
-      <c r="E492" s="6" t="inlineStr">
+      <c r="F492" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31645,9 +33124,12 @@
         </is>
       </c>
       <c r="D493" s="4">
+        <v>10</v>
+      </c>
+      <c r="E493" s="4">
         <v>2</v>
       </c>
-      <c r="E493" s="6" t="inlineStr">
+      <c r="F493" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31723,9 +33205,12 @@
         </is>
       </c>
       <c r="D494" s="4">
+        <v>10</v>
+      </c>
+      <c r="E494" s="4">
         <v>3</v>
       </c>
-      <c r="E494" s="6" t="inlineStr">
+      <c r="F494" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31801,9 +33286,12 @@
         </is>
       </c>
       <c r="D495" s="4">
+        <v>10</v>
+      </c>
+      <c r="E495" s="4">
         <v>4</v>
       </c>
-      <c r="E495" s="6" t="inlineStr">
+      <c r="F495" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31879,9 +33367,12 @@
         </is>
       </c>
       <c r="D496" s="4">
+        <v>10</v>
+      </c>
+      <c r="E496" s="4">
         <v>5</v>
       </c>
-      <c r="E496" s="6" t="inlineStr">
+      <c r="F496" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -31957,9 +33448,12 @@
         </is>
       </c>
       <c r="D497" s="4">
+        <v>10</v>
+      </c>
+      <c r="E497" s="4">
         <v>6</v>
       </c>
-      <c r="E497" s="6" t="inlineStr">
+      <c r="F497" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32035,9 +33529,12 @@
         </is>
       </c>
       <c r="D498" s="4">
+        <v>10</v>
+      </c>
+      <c r="E498" s="4">
         <v>7</v>
       </c>
-      <c r="E498" s="6" t="inlineStr">
+      <c r="F498" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32113,9 +33610,12 @@
         </is>
       </c>
       <c r="D499" s="4">
+        <v>10</v>
+      </c>
+      <c r="E499" s="4">
         <v>8</v>
       </c>
-      <c r="E499" s="6" t="inlineStr">
+      <c r="F499" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32191,9 +33691,12 @@
         </is>
       </c>
       <c r="D500" s="4">
+        <v>10</v>
+      </c>
+      <c r="E500" s="4">
         <v>9</v>
       </c>
-      <c r="E500" s="6" t="inlineStr">
+      <c r="F500" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32271,7 +33774,10 @@
       <c r="D501" s="4">
         <v>10</v>
       </c>
-      <c r="E501" s="6" t="inlineStr">
+      <c r="E501" s="4">
+        <v>10</v>
+      </c>
+      <c r="F501" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32349,7 +33855,10 @@
       <c r="D502" s="4">
         <v>1</v>
       </c>
-      <c r="E502" s="6" t="inlineStr">
+      <c r="E502" s="4">
+        <v>1</v>
+      </c>
+      <c r="F502" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32419,9 +33928,12 @@
         </is>
       </c>
       <c r="D503" s="4">
+        <v>5</v>
+      </c>
+      <c r="E503" s="4">
         <v>1</v>
       </c>
-      <c r="E503" s="6" t="inlineStr">
+      <c r="F503" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32482,9 +33994,12 @@
         </is>
       </c>
       <c r="D504" s="4">
+        <v>5</v>
+      </c>
+      <c r="E504" s="4">
         <v>2</v>
       </c>
-      <c r="E504" s="6" t="inlineStr">
+      <c r="F504" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32545,9 +34060,12 @@
         </is>
       </c>
       <c r="D505" s="4">
+        <v>5</v>
+      </c>
+      <c r="E505" s="4">
         <v>3</v>
       </c>
-      <c r="E505" s="6" t="inlineStr">
+      <c r="F505" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32608,9 +34126,12 @@
         </is>
       </c>
       <c r="D506" s="4">
+        <v>5</v>
+      </c>
+      <c r="E506" s="4">
         <v>4</v>
       </c>
-      <c r="E506" s="6" t="inlineStr">
+      <c r="F506" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32673,7 +34194,10 @@
       <c r="D507" s="4">
         <v>5</v>
       </c>
-      <c r="E507" s="6" t="inlineStr">
+      <c r="E507" s="4">
+        <v>5</v>
+      </c>
+      <c r="F507" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32736,7 +34260,10 @@
       <c r="D508" s="4">
         <v>1</v>
       </c>
-      <c r="E508" s="6" t="inlineStr">
+      <c r="E508" s="4">
+        <v>1</v>
+      </c>
+      <c r="F508" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32805,9 +34332,12 @@
         </is>
       </c>
       <c r="D509" s="4">
+        <v>4</v>
+      </c>
+      <c r="E509" s="4">
         <v>1</v>
       </c>
-      <c r="E509" s="6" t="inlineStr">
+      <c r="F509" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32868,9 +34398,12 @@
         </is>
       </c>
       <c r="D510" s="4">
+        <v>4</v>
+      </c>
+      <c r="E510" s="4">
         <v>2</v>
       </c>
-      <c r="E510" s="6" t="inlineStr">
+      <c r="F510" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32931,9 +34464,12 @@
         </is>
       </c>
       <c r="D511" s="4">
+        <v>4</v>
+      </c>
+      <c r="E511" s="4">
         <v>3</v>
       </c>
-      <c r="E511" s="6" t="inlineStr">
+      <c r="F511" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -32996,7 +34532,10 @@
       <c r="D512" s="4">
         <v>4</v>
       </c>
-      <c r="E512" s="6" t="inlineStr">
+      <c r="E512" s="4">
+        <v>4</v>
+      </c>
+      <c r="F512" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33057,9 +34596,12 @@
         </is>
       </c>
       <c r="D513" s="4">
+        <v>2</v>
+      </c>
+      <c r="E513" s="4">
         <v>1</v>
       </c>
-      <c r="E513" s="6" t="inlineStr">
+      <c r="F513" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33129,9 +34671,12 @@
         </is>
       </c>
       <c r="D514" s="4">
+        <v>2</v>
+      </c>
+      <c r="E514" s="4">
         <v>1</v>
       </c>
-      <c r="E514" s="6" t="inlineStr">
+      <c r="F514" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33203,7 +34748,10 @@
       <c r="D515" s="4">
         <v>2</v>
       </c>
-      <c r="E515" s="6" t="inlineStr">
+      <c r="E515" s="4">
+        <v>2</v>
+      </c>
+      <c r="F515" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33273,9 +34821,12 @@
         </is>
       </c>
       <c r="D516" s="4">
+        <v>2</v>
+      </c>
+      <c r="E516" s="4">
         <v>1</v>
       </c>
-      <c r="E516" s="6" t="inlineStr">
+      <c r="F516" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33347,7 +34898,10 @@
       <c r="D517" s="4">
         <v>2</v>
       </c>
-      <c r="E517" s="6" t="inlineStr">
+      <c r="E517" s="4">
+        <v>2</v>
+      </c>
+      <c r="F517" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33419,7 +34973,10 @@
       <c r="D518" s="4">
         <v>1</v>
       </c>
-      <c r="E518" s="6" t="inlineStr">
+      <c r="E518" s="4">
+        <v>1</v>
+      </c>
+      <c r="F518" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33475,7 +35032,10 @@
       <c r="D519" s="4">
         <v>1</v>
       </c>
-      <c r="E519" s="6" t="inlineStr">
+      <c r="E519" s="4">
+        <v>1</v>
+      </c>
+      <c r="F519" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33529,9 +35089,12 @@
         </is>
       </c>
       <c r="D520" s="4">
+        <v>4</v>
+      </c>
+      <c r="E520" s="4">
         <v>1</v>
       </c>
-      <c r="E520" s="6" t="inlineStr">
+      <c r="F520" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33601,9 +35164,12 @@
         </is>
       </c>
       <c r="D521" s="4">
+        <v>4</v>
+      </c>
+      <c r="E521" s="4">
         <v>2</v>
       </c>
-      <c r="E521" s="6" t="inlineStr">
+      <c r="F521" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33673,9 +35239,12 @@
         </is>
       </c>
       <c r="D522" s="4">
+        <v>4</v>
+      </c>
+      <c r="E522" s="4">
         <v>3</v>
       </c>
-      <c r="E522" s="6" t="inlineStr">
+      <c r="F522" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33747,7 +35316,10 @@
       <c r="D523" s="4">
         <v>4</v>
       </c>
-      <c r="E523" s="6" t="inlineStr">
+      <c r="E523" s="4">
+        <v>4</v>
+      </c>
+      <c r="F523" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33817,9 +35389,12 @@
         </is>
       </c>
       <c r="D524" s="4">
+        <v>6</v>
+      </c>
+      <c r="E524" s="4">
         <v>1</v>
       </c>
-      <c r="E524" s="6" t="inlineStr">
+      <c r="F524" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33880,9 +35455,12 @@
         </is>
       </c>
       <c r="D525" s="4">
+        <v>6</v>
+      </c>
+      <c r="E525" s="4">
         <v>2</v>
       </c>
-      <c r="E525" s="6" t="inlineStr">
+      <c r="F525" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -33943,9 +35521,12 @@
         </is>
       </c>
       <c r="D526" s="4">
+        <v>6</v>
+      </c>
+      <c r="E526" s="4">
         <v>3</v>
       </c>
-      <c r="E526" s="6" t="inlineStr">
+      <c r="F526" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34006,9 +35587,12 @@
         </is>
       </c>
       <c r="D527" s="4">
+        <v>6</v>
+      </c>
+      <c r="E527" s="4">
         <v>4</v>
       </c>
-      <c r="E527" s="6" t="inlineStr">
+      <c r="F527" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34069,9 +35653,12 @@
         </is>
       </c>
       <c r="D528" s="4">
+        <v>6</v>
+      </c>
+      <c r="E528" s="4">
         <v>5</v>
       </c>
-      <c r="E528" s="6" t="inlineStr">
+      <c r="F528" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34134,7 +35721,10 @@
       <c r="D529" s="4">
         <v>6</v>
       </c>
-      <c r="E529" s="6" t="inlineStr">
+      <c r="E529" s="4">
+        <v>6</v>
+      </c>
+      <c r="F529" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34197,7 +35787,10 @@
       <c r="D530" s="4">
         <v>1</v>
       </c>
-      <c r="E530" s="6" t="inlineStr">
+      <c r="E530" s="4">
+        <v>1</v>
+      </c>
+      <c r="F530" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34258,9 +35851,12 @@
         </is>
       </c>
       <c r="D531" s="4">
+        <v>2</v>
+      </c>
+      <c r="E531" s="4">
         <v>1</v>
       </c>
-      <c r="E531" s="6" t="inlineStr">
+      <c r="F531" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34331,7 +35927,10 @@
       <c r="D532" s="4">
         <v>2</v>
       </c>
-      <c r="E532" s="6" t="inlineStr">
+      <c r="E532" s="4">
+        <v>2</v>
+      </c>
+      <c r="F532" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34400,9 +35999,12 @@
         </is>
       </c>
       <c r="D533" s="4">
+        <v>4</v>
+      </c>
+      <c r="E533" s="4">
         <v>1</v>
       </c>
-      <c r="E533" s="6" t="inlineStr">
+      <c r="F533" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34463,9 +36065,12 @@
         </is>
       </c>
       <c r="D534" s="4">
+        <v>4</v>
+      </c>
+      <c r="E534" s="4">
         <v>2</v>
       </c>
-      <c r="E534" s="6" t="inlineStr">
+      <c r="F534" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34526,9 +36131,12 @@
         </is>
       </c>
       <c r="D535" s="4">
+        <v>4</v>
+      </c>
+      <c r="E535" s="4">
         <v>3</v>
       </c>
-      <c r="E535" s="6" t="inlineStr">
+      <c r="F535" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34591,7 +36199,10 @@
       <c r="D536" s="4">
         <v>4</v>
       </c>
-      <c r="E536" s="6" t="inlineStr">
+      <c r="E536" s="4">
+        <v>4</v>
+      </c>
+      <c r="F536" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34654,7 +36265,10 @@
       <c r="D537" s="4">
         <v>1</v>
       </c>
-      <c r="E537" s="6" t="inlineStr">
+      <c r="E537" s="4">
+        <v>1</v>
+      </c>
+      <c r="F537" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34725,7 +36339,10 @@
       <c r="D538" s="4">
         <v>1</v>
       </c>
-      <c r="E538" s="6" t="inlineStr">
+      <c r="E538" s="4">
+        <v>1</v>
+      </c>
+      <c r="F538" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34809,9 +36426,12 @@
         </is>
       </c>
       <c r="D539" s="4">
+        <v>2</v>
+      </c>
+      <c r="E539" s="4">
         <v>1</v>
       </c>
-      <c r="E539" s="6" t="inlineStr">
+      <c r="F539" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34883,7 +36503,10 @@
       <c r="D540" s="4">
         <v>2</v>
       </c>
-      <c r="E540" s="6" t="inlineStr">
+      <c r="E540" s="4">
+        <v>2</v>
+      </c>
+      <c r="F540" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -34953,9 +36576,12 @@
         </is>
       </c>
       <c r="D541" s="4">
+        <v>3</v>
+      </c>
+      <c r="E541" s="4">
         <v>1</v>
       </c>
-      <c r="E541" s="6" t="inlineStr">
+      <c r="F541" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35016,9 +36642,12 @@
         </is>
       </c>
       <c r="D542" s="4">
+        <v>3</v>
+      </c>
+      <c r="E542" s="4">
         <v>2</v>
       </c>
-      <c r="E542" s="6" t="inlineStr">
+      <c r="F542" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35081,7 +36710,10 @@
       <c r="D543" s="4">
         <v>3</v>
       </c>
-      <c r="E543" s="6" t="inlineStr">
+      <c r="E543" s="4">
+        <v>3</v>
+      </c>
+      <c r="F543" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35144,7 +36776,10 @@
       <c r="D544" s="4">
         <v>1</v>
       </c>
-      <c r="E544" s="6" t="inlineStr">
+      <c r="E544" s="4">
+        <v>1</v>
+      </c>
+      <c r="F544" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35215,7 +36850,10 @@
       <c r="D545" s="4">
         <v>1</v>
       </c>
-      <c r="E545" s="6" t="inlineStr">
+      <c r="E545" s="4">
+        <v>1</v>
+      </c>
+      <c r="F545" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35285,9 +36923,12 @@
         </is>
       </c>
       <c r="D546" s="4">
+        <v>2</v>
+      </c>
+      <c r="E546" s="4">
         <v>1</v>
       </c>
-      <c r="E546" s="6" t="inlineStr">
+      <c r="F546" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35350,7 +36991,10 @@
       <c r="D547" s="4">
         <v>2</v>
       </c>
-      <c r="E547" s="6" t="inlineStr">
+      <c r="E547" s="4">
+        <v>2</v>
+      </c>
+      <c r="F547" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35413,7 +37057,10 @@
       <c r="D548" s="4">
         <v>1</v>
       </c>
-      <c r="E548" s="6" t="inlineStr">
+      <c r="E548" s="4">
+        <v>1</v>
+      </c>
+      <c r="F548" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35474,9 +37121,12 @@
         </is>
       </c>
       <c r="D549" s="4">
+        <v>6</v>
+      </c>
+      <c r="E549" s="4">
         <v>1</v>
       </c>
-      <c r="E549" s="6" t="inlineStr">
+      <c r="F549" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35537,9 +37187,12 @@
         </is>
       </c>
       <c r="D550" s="4">
+        <v>6</v>
+      </c>
+      <c r="E550" s="4">
         <v>2</v>
       </c>
-      <c r="E550" s="6" t="inlineStr">
+      <c r="F550" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35600,9 +37253,12 @@
         </is>
       </c>
       <c r="D551" s="4">
+        <v>6</v>
+      </c>
+      <c r="E551" s="4">
         <v>3</v>
       </c>
-      <c r="E551" s="6" t="inlineStr">
+      <c r="F551" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35663,9 +37319,12 @@
         </is>
       </c>
       <c r="D552" s="4">
+        <v>6</v>
+      </c>
+      <c r="E552" s="4">
         <v>4</v>
       </c>
-      <c r="E552" s="6" t="inlineStr">
+      <c r="F552" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35726,9 +37385,12 @@
         </is>
       </c>
       <c r="D553" s="4">
+        <v>6</v>
+      </c>
+      <c r="E553" s="4">
         <v>5</v>
       </c>
-      <c r="E553" s="6" t="inlineStr">
+      <c r="F553" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35791,7 +37453,10 @@
       <c r="D554" s="4">
         <v>6</v>
       </c>
-      <c r="E554" s="6" t="inlineStr">
+      <c r="E554" s="4">
+        <v>6</v>
+      </c>
+      <c r="F554" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35852,9 +37517,12 @@
         </is>
       </c>
       <c r="D555" s="4">
+        <v>41</v>
+      </c>
+      <c r="E555" s="4">
         <v>1</v>
       </c>
-      <c r="E555" s="6" t="inlineStr">
+      <c r="F555" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35924,9 +37592,12 @@
         </is>
       </c>
       <c r="D556" s="4">
+        <v>41</v>
+      </c>
+      <c r="E556" s="4">
         <v>2</v>
       </c>
-      <c r="E556" s="6" t="inlineStr">
+      <c r="F556" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -35996,9 +37667,12 @@
         </is>
       </c>
       <c r="D557" s="4">
+        <v>41</v>
+      </c>
+      <c r="E557" s="4">
         <v>3</v>
       </c>
-      <c r="E557" s="6" t="inlineStr">
+      <c r="F557" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36068,9 +37742,12 @@
         </is>
       </c>
       <c r="D558" s="4">
+        <v>41</v>
+      </c>
+      <c r="E558" s="4">
         <v>4</v>
       </c>
-      <c r="E558" s="6" t="inlineStr">
+      <c r="F558" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36140,9 +37817,12 @@
         </is>
       </c>
       <c r="D559" s="4">
+        <v>41</v>
+      </c>
+      <c r="E559" s="4">
         <v>5</v>
       </c>
-      <c r="E559" s="6" t="inlineStr">
+      <c r="F559" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36212,9 +37892,12 @@
         </is>
       </c>
       <c r="D560" s="4">
+        <v>41</v>
+      </c>
+      <c r="E560" s="4">
         <v>6</v>
       </c>
-      <c r="E560" s="6" t="inlineStr">
+      <c r="F560" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36284,9 +37967,12 @@
         </is>
       </c>
       <c r="D561" s="4">
+        <v>41</v>
+      </c>
+      <c r="E561" s="4">
         <v>7</v>
       </c>
-      <c r="E561" s="6" t="inlineStr">
+      <c r="F561" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36356,9 +38042,12 @@
         </is>
       </c>
       <c r="D562" s="4">
+        <v>41</v>
+      </c>
+      <c r="E562" s="4">
         <v>8</v>
       </c>
-      <c r="E562" s="6" t="inlineStr">
+      <c r="F562" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36428,9 +38117,12 @@
         </is>
       </c>
       <c r="D563" s="4">
+        <v>41</v>
+      </c>
+      <c r="E563" s="4">
         <v>9</v>
       </c>
-      <c r="E563" s="6" t="inlineStr">
+      <c r="F563" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36500,9 +38192,12 @@
         </is>
       </c>
       <c r="D564" s="4">
+        <v>41</v>
+      </c>
+      <c r="E564" s="4">
         <v>10</v>
       </c>
-      <c r="E564" s="6" t="inlineStr">
+      <c r="F564" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36572,9 +38267,12 @@
         </is>
       </c>
       <c r="D565" s="4">
+        <v>41</v>
+      </c>
+      <c r="E565" s="4">
         <v>11</v>
       </c>
-      <c r="E565" s="6" t="inlineStr">
+      <c r="F565" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36644,9 +38342,12 @@
         </is>
       </c>
       <c r="D566" s="4">
+        <v>41</v>
+      </c>
+      <c r="E566" s="4">
         <v>12</v>
       </c>
-      <c r="E566" s="6" t="inlineStr">
+      <c r="F566" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36716,9 +38417,12 @@
         </is>
       </c>
       <c r="D567" s="4">
+        <v>41</v>
+      </c>
+      <c r="E567" s="4">
         <v>13</v>
       </c>
-      <c r="E567" s="6" t="inlineStr">
+      <c r="F567" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36788,9 +38492,12 @@
         </is>
       </c>
       <c r="D568" s="4">
+        <v>41</v>
+      </c>
+      <c r="E568" s="4">
         <v>14</v>
       </c>
-      <c r="E568" s="6" t="inlineStr">
+      <c r="F568" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36860,9 +38567,12 @@
         </is>
       </c>
       <c r="D569" s="4">
+        <v>41</v>
+      </c>
+      <c r="E569" s="4">
         <v>15</v>
       </c>
-      <c r="E569" s="6" t="inlineStr">
+      <c r="F569" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -36932,9 +38642,12 @@
         </is>
       </c>
       <c r="D570" s="4">
+        <v>41</v>
+      </c>
+      <c r="E570" s="4">
         <v>16</v>
       </c>
-      <c r="E570" s="6" t="inlineStr">
+      <c r="F570" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37004,9 +38717,12 @@
         </is>
       </c>
       <c r="D571" s="4">
+        <v>41</v>
+      </c>
+      <c r="E571" s="4">
         <v>17</v>
       </c>
-      <c r="E571" s="6" t="inlineStr">
+      <c r="F571" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37076,9 +38792,12 @@
         </is>
       </c>
       <c r="D572" s="4">
+        <v>41</v>
+      </c>
+      <c r="E572" s="4">
         <v>18</v>
       </c>
-      <c r="E572" s="6" t="inlineStr">
+      <c r="F572" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37148,9 +38867,12 @@
         </is>
       </c>
       <c r="D573" s="4">
+        <v>41</v>
+      </c>
+      <c r="E573" s="4">
         <v>19</v>
       </c>
-      <c r="E573" s="6" t="inlineStr">
+      <c r="F573" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37220,9 +38942,12 @@
         </is>
       </c>
       <c r="D574" s="4">
+        <v>41</v>
+      </c>
+      <c r="E574" s="4">
         <v>20</v>
       </c>
-      <c r="E574" s="6" t="inlineStr">
+      <c r="F574" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37292,9 +39017,12 @@
         </is>
       </c>
       <c r="D575" s="4">
+        <v>9</v>
+      </c>
+      <c r="E575" s="4">
         <v>1</v>
       </c>
-      <c r="E575" s="6" t="inlineStr">
+      <c r="F575" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37364,9 +39092,12 @@
         </is>
       </c>
       <c r="D576" s="4">
+        <v>9</v>
+      </c>
+      <c r="E576" s="4">
         <v>2</v>
       </c>
-      <c r="E576" s="6" t="inlineStr">
+      <c r="F576" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37436,9 +39167,12 @@
         </is>
       </c>
       <c r="D577" s="4">
+        <v>9</v>
+      </c>
+      <c r="E577" s="4">
         <v>3</v>
       </c>
-      <c r="E577" s="6" t="inlineStr">
+      <c r="F577" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37508,9 +39242,12 @@
         </is>
       </c>
       <c r="D578" s="4">
+        <v>9</v>
+      </c>
+      <c r="E578" s="4">
         <v>4</v>
       </c>
-      <c r="E578" s="6" t="inlineStr">
+      <c r="F578" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37580,9 +39317,12 @@
         </is>
       </c>
       <c r="D579" s="4">
+        <v>9</v>
+      </c>
+      <c r="E579" s="4">
         <v>5</v>
       </c>
-      <c r="E579" s="6" t="inlineStr">
+      <c r="F579" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37652,9 +39392,12 @@
         </is>
       </c>
       <c r="D580" s="4">
+        <v>9</v>
+      </c>
+      <c r="E580" s="4">
         <v>6</v>
       </c>
-      <c r="E580" s="6" t="inlineStr">
+      <c r="F580" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37724,9 +39467,12 @@
         </is>
       </c>
       <c r="D581" s="4">
+        <v>9</v>
+      </c>
+      <c r="E581" s="4">
         <v>7</v>
       </c>
-      <c r="E581" s="6" t="inlineStr">
+      <c r="F581" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37796,9 +39542,12 @@
         </is>
       </c>
       <c r="D582" s="4">
+        <v>9</v>
+      </c>
+      <c r="E582" s="4">
         <v>8</v>
       </c>
-      <c r="E582" s="6" t="inlineStr">
+      <c r="F582" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37868,9 +39617,12 @@
         </is>
       </c>
       <c r="D583" s="4">
+        <v>6</v>
+      </c>
+      <c r="E583" s="4">
         <v>1</v>
       </c>
-      <c r="E583" s="6" t="inlineStr">
+      <c r="F583" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -37940,9 +39692,12 @@
         </is>
       </c>
       <c r="D584" s="4">
+        <v>6</v>
+      </c>
+      <c r="E584" s="4">
         <v>2</v>
       </c>
-      <c r="E584" s="6" t="inlineStr">
+      <c r="F584" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38012,9 +39767,12 @@
         </is>
       </c>
       <c r="D585" s="4">
+        <v>6</v>
+      </c>
+      <c r="E585" s="4">
         <v>3</v>
       </c>
-      <c r="E585" s="6" t="inlineStr">
+      <c r="F585" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38084,9 +39842,12 @@
         </is>
       </c>
       <c r="D586" s="4">
+        <v>6</v>
+      </c>
+      <c r="E586" s="4">
         <v>4</v>
       </c>
-      <c r="E586" s="6" t="inlineStr">
+      <c r="F586" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38156,9 +39917,12 @@
         </is>
       </c>
       <c r="D587" s="4">
+        <v>6</v>
+      </c>
+      <c r="E587" s="4">
         <v>5</v>
       </c>
-      <c r="E587" s="6" t="inlineStr">
+      <c r="F587" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38230,7 +39994,10 @@
       <c r="D588" s="4">
         <v>6</v>
       </c>
-      <c r="E588" s="6" t="inlineStr">
+      <c r="E588" s="4">
+        <v>6</v>
+      </c>
+      <c r="F588" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38300,9 +40067,12 @@
         </is>
       </c>
       <c r="D589" s="4">
+        <v>7</v>
+      </c>
+      <c r="E589" s="4">
         <v>1</v>
       </c>
-      <c r="E589" s="6" t="inlineStr">
+      <c r="F589" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38372,9 +40142,12 @@
         </is>
       </c>
       <c r="D590" s="4">
+        <v>7</v>
+      </c>
+      <c r="E590" s="4">
         <v>2</v>
       </c>
-      <c r="E590" s="6" t="inlineStr">
+      <c r="F590" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38444,9 +40217,12 @@
         </is>
       </c>
       <c r="D591" s="4">
+        <v>7</v>
+      </c>
+      <c r="E591" s="4">
         <v>3</v>
       </c>
-      <c r="E591" s="6" t="inlineStr">
+      <c r="F591" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38516,9 +40292,12 @@
         </is>
       </c>
       <c r="D592" s="4">
+        <v>7</v>
+      </c>
+      <c r="E592" s="4">
         <v>4</v>
       </c>
-      <c r="E592" s="6" t="inlineStr">
+      <c r="F592" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38588,9 +40367,12 @@
         </is>
       </c>
       <c r="D593" s="4">
+        <v>7</v>
+      </c>
+      <c r="E593" s="4">
         <v>5</v>
       </c>
-      <c r="E593" s="6" t="inlineStr">
+      <c r="F593" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38660,9 +40442,12 @@
         </is>
       </c>
       <c r="D594" s="4">
+        <v>7</v>
+      </c>
+      <c r="E594" s="4">
         <v>6</v>
       </c>
-      <c r="E594" s="6" t="inlineStr">
+      <c r="F594" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38734,7 +40519,10 @@
       <c r="D595" s="4">
         <v>7</v>
       </c>
-      <c r="E595" s="6" t="inlineStr">
+      <c r="E595" s="4">
+        <v>7</v>
+      </c>
+      <c r="F595" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38804,9 +40592,12 @@
         </is>
       </c>
       <c r="D596" s="4">
+        <v>3</v>
+      </c>
+      <c r="E596" s="4">
         <v>1</v>
       </c>
-      <c r="E596" s="6" t="inlineStr">
+      <c r="F596" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38876,9 +40667,12 @@
         </is>
       </c>
       <c r="D597" s="4">
+        <v>3</v>
+      </c>
+      <c r="E597" s="4">
         <v>2</v>
       </c>
-      <c r="E597" s="6" t="inlineStr">
+      <c r="F597" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -38950,7 +40744,10 @@
       <c r="D598" s="4">
         <v>3</v>
       </c>
-      <c r="E598" s="6" t="inlineStr">
+      <c r="E598" s="4">
+        <v>3</v>
+      </c>
+      <c r="F598" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39020,9 +40817,12 @@
         </is>
       </c>
       <c r="D599" s="4">
+        <v>4</v>
+      </c>
+      <c r="E599" s="4">
         <v>1</v>
       </c>
-      <c r="E599" s="6" t="inlineStr">
+      <c r="F599" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39092,9 +40892,12 @@
         </is>
       </c>
       <c r="D600" s="4">
+        <v>4</v>
+      </c>
+      <c r="E600" s="4">
         <v>2</v>
       </c>
-      <c r="E600" s="6" t="inlineStr">
+      <c r="F600" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39164,9 +40967,12 @@
         </is>
       </c>
       <c r="D601" s="4">
+        <v>4</v>
+      </c>
+      <c r="E601" s="4">
         <v>3</v>
       </c>
-      <c r="E601" s="6" t="inlineStr">
+      <c r="F601" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39238,7 +41044,10 @@
       <c r="D602" s="4">
         <v>4</v>
       </c>
-      <c r="E602" s="6" t="inlineStr">
+      <c r="E602" s="4">
+        <v>4</v>
+      </c>
+      <c r="F602" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39308,9 +41117,12 @@
         </is>
       </c>
       <c r="D603" s="4">
+        <v>5</v>
+      </c>
+      <c r="E603" s="4">
         <v>1</v>
       </c>
-      <c r="E603" s="6" t="inlineStr">
+      <c r="F603" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39380,9 +41192,12 @@
         </is>
       </c>
       <c r="D604" s="4">
+        <v>5</v>
+      </c>
+      <c r="E604" s="4">
         <v>2</v>
       </c>
-      <c r="E604" s="6" t="inlineStr">
+      <c r="F604" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39452,9 +41267,12 @@
         </is>
       </c>
       <c r="D605" s="4">
+        <v>5</v>
+      </c>
+      <c r="E605" s="4">
         <v>3</v>
       </c>
-      <c r="E605" s="6" t="inlineStr">
+      <c r="F605" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39524,9 +41342,12 @@
         </is>
       </c>
       <c r="D606" s="4">
+        <v>5</v>
+      </c>
+      <c r="E606" s="4">
         <v>4</v>
       </c>
-      <c r="E606" s="6" t="inlineStr">
+      <c r="F606" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39598,7 +41419,10 @@
       <c r="D607" s="4">
         <v>5</v>
       </c>
-      <c r="E607" s="6" t="inlineStr">
+      <c r="E607" s="4">
+        <v>5</v>
+      </c>
+      <c r="F607" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39668,9 +41492,12 @@
         </is>
       </c>
       <c r="D608" s="4">
+        <v>3</v>
+      </c>
+      <c r="E608" s="4">
         <v>1</v>
       </c>
-      <c r="E608" s="6" t="inlineStr">
+      <c r="F608" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39740,9 +41567,12 @@
         </is>
       </c>
       <c r="D609" s="4">
+        <v>3</v>
+      </c>
+      <c r="E609" s="4">
         <v>2</v>
       </c>
-      <c r="E609" s="6" t="inlineStr">
+      <c r="F609" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39814,7 +41644,10 @@
       <c r="D610" s="4">
         <v>3</v>
       </c>
-      <c r="E610" s="6" t="inlineStr">
+      <c r="E610" s="4">
+        <v>3</v>
+      </c>
+      <c r="F610" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39884,9 +41717,12 @@
         </is>
       </c>
       <c r="D611" s="4">
+        <v>2</v>
+      </c>
+      <c r="E611" s="4">
         <v>1</v>
       </c>
-      <c r="E611" s="6" t="inlineStr">
+      <c r="F611" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -39958,7 +41794,10 @@
       <c r="D612" s="4">
         <v>2</v>
       </c>
-      <c r="E612" s="6" t="inlineStr">
+      <c r="E612" s="4">
+        <v>2</v>
+      </c>
+      <c r="F612" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40028,9 +41867,12 @@
         </is>
       </c>
       <c r="D613" s="4">
+        <v>3</v>
+      </c>
+      <c r="E613" s="4">
         <v>1</v>
       </c>
-      <c r="E613" s="6" t="inlineStr">
+      <c r="F613" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40100,9 +41942,12 @@
         </is>
       </c>
       <c r="D614" s="4">
+        <v>3</v>
+      </c>
+      <c r="E614" s="4">
         <v>2</v>
       </c>
-      <c r="E614" s="6" t="inlineStr">
+      <c r="F614" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40174,7 +42019,10 @@
       <c r="D615" s="4">
         <v>3</v>
       </c>
-      <c r="E615" s="6" t="inlineStr">
+      <c r="E615" s="4">
+        <v>3</v>
+      </c>
+      <c r="F615" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40244,9 +42092,12 @@
         </is>
       </c>
       <c r="D616" s="4">
+        <v>6</v>
+      </c>
+      <c r="E616" s="4">
         <v>1</v>
       </c>
-      <c r="E616" s="6" t="inlineStr">
+      <c r="F616" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40316,9 +42167,12 @@
         </is>
       </c>
       <c r="D617" s="4">
+        <v>6</v>
+      </c>
+      <c r="E617" s="4">
         <v>2</v>
       </c>
-      <c r="E617" s="6" t="inlineStr">
+      <c r="F617" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40388,9 +42242,12 @@
         </is>
       </c>
       <c r="D618" s="4">
+        <v>6</v>
+      </c>
+      <c r="E618" s="4">
         <v>3</v>
       </c>
-      <c r="E618" s="6" t="inlineStr">
+      <c r="F618" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40460,9 +42317,12 @@
         </is>
       </c>
       <c r="D619" s="4">
+        <v>6</v>
+      </c>
+      <c r="E619" s="4">
         <v>4</v>
       </c>
-      <c r="E619" s="6" t="inlineStr">
+      <c r="F619" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40532,9 +42392,12 @@
         </is>
       </c>
       <c r="D620" s="4">
+        <v>6</v>
+      </c>
+      <c r="E620" s="4">
         <v>5</v>
       </c>
-      <c r="E620" s="6" t="inlineStr">
+      <c r="F620" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40606,7 +42469,10 @@
       <c r="D621" s="4">
         <v>6</v>
       </c>
-      <c r="E621" s="6" t="inlineStr">
+      <c r="E621" s="4">
+        <v>6</v>
+      </c>
+      <c r="F621" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40678,7 +42544,10 @@
       <c r="D622" s="4">
         <v>1</v>
       </c>
-      <c r="E622" s="6" t="inlineStr">
+      <c r="E622" s="4">
+        <v>1</v>
+      </c>
+      <c r="F622" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40748,9 +42617,12 @@
         </is>
       </c>
       <c r="D623" s="4">
+        <v>18</v>
+      </c>
+      <c r="E623" s="4">
         <v>1</v>
       </c>
-      <c r="E623" s="6" t="inlineStr">
+      <c r="F623" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40820,9 +42692,12 @@
         </is>
       </c>
       <c r="D624" s="4">
+        <v>18</v>
+      </c>
+      <c r="E624" s="4">
         <v>2</v>
       </c>
-      <c r="E624" s="6" t="inlineStr">
+      <c r="F624" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40892,9 +42767,12 @@
         </is>
       </c>
       <c r="D625" s="4">
+        <v>18</v>
+      </c>
+      <c r="E625" s="4">
         <v>3</v>
       </c>
-      <c r="E625" s="6" t="inlineStr">
+      <c r="F625" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -40964,9 +42842,12 @@
         </is>
       </c>
       <c r="D626" s="4">
+        <v>18</v>
+      </c>
+      <c r="E626" s="4">
         <v>4</v>
       </c>
-      <c r="E626" s="6" t="inlineStr">
+      <c r="F626" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41036,9 +42917,12 @@
         </is>
       </c>
       <c r="D627" s="4">
+        <v>18</v>
+      </c>
+      <c r="E627" s="4">
         <v>5</v>
       </c>
-      <c r="E627" s="6" t="inlineStr">
+      <c r="F627" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41108,9 +42992,12 @@
         </is>
       </c>
       <c r="D628" s="4">
+        <v>18</v>
+      </c>
+      <c r="E628" s="4">
         <v>6</v>
       </c>
-      <c r="E628" s="6" t="inlineStr">
+      <c r="F628" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41180,9 +43067,12 @@
         </is>
       </c>
       <c r="D629" s="4">
+        <v>18</v>
+      </c>
+      <c r="E629" s="4">
         <v>7</v>
       </c>
-      <c r="E629" s="6" t="inlineStr">
+      <c r="F629" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41252,9 +43142,12 @@
         </is>
       </c>
       <c r="D630" s="4">
+        <v>18</v>
+      </c>
+      <c r="E630" s="4">
         <v>8</v>
       </c>
-      <c r="E630" s="6" t="inlineStr">
+      <c r="F630" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41324,9 +43217,12 @@
         </is>
       </c>
       <c r="D631" s="4">
+        <v>18</v>
+      </c>
+      <c r="E631" s="4">
         <v>9</v>
       </c>
-      <c r="E631" s="6" t="inlineStr">
+      <c r="F631" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41396,9 +43292,12 @@
         </is>
       </c>
       <c r="D632" s="4">
+        <v>18</v>
+      </c>
+      <c r="E632" s="4">
         <v>10</v>
       </c>
-      <c r="E632" s="6" t="inlineStr">
+      <c r="F632" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41468,9 +43367,12 @@
         </is>
       </c>
       <c r="D633" s="4">
+        <v>18</v>
+      </c>
+      <c r="E633" s="4">
         <v>11</v>
       </c>
-      <c r="E633" s="6" t="inlineStr">
+      <c r="F633" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41540,9 +43442,12 @@
         </is>
       </c>
       <c r="D634" s="4">
+        <v>18</v>
+      </c>
+      <c r="E634" s="4">
         <v>12</v>
       </c>
-      <c r="E634" s="6" t="inlineStr">
+      <c r="F634" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41612,9 +43517,12 @@
         </is>
       </c>
       <c r="D635" s="4">
+        <v>18</v>
+      </c>
+      <c r="E635" s="4">
         <v>13</v>
       </c>
-      <c r="E635" s="6" t="inlineStr">
+      <c r="F635" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41684,9 +43592,12 @@
         </is>
       </c>
       <c r="D636" s="4">
+        <v>18</v>
+      </c>
+      <c r="E636" s="4">
         <v>14</v>
       </c>
-      <c r="E636" s="6" t="inlineStr">
+      <c r="F636" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41756,9 +43667,12 @@
         </is>
       </c>
       <c r="D637" s="4">
+        <v>18</v>
+      </c>
+      <c r="E637" s="4">
         <v>15</v>
       </c>
-      <c r="E637" s="6" t="inlineStr">
+      <c r="F637" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41828,9 +43742,12 @@
         </is>
       </c>
       <c r="D638" s="4">
+        <v>18</v>
+      </c>
+      <c r="E638" s="4">
         <v>16</v>
       </c>
-      <c r="E638" s="6" t="inlineStr">
+      <c r="F638" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41900,9 +43817,12 @@
         </is>
       </c>
       <c r="D639" s="4">
+        <v>18</v>
+      </c>
+      <c r="E639" s="4">
         <v>17</v>
       </c>
-      <c r="E639" s="6" t="inlineStr">
+      <c r="F639" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -41974,7 +43894,10 @@
       <c r="D640" s="4">
         <v>18</v>
       </c>
-      <c r="E640" s="6" t="inlineStr">
+      <c r="E640" s="4">
+        <v>18</v>
+      </c>
+      <c r="F640" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42044,9 +43967,12 @@
         </is>
       </c>
       <c r="D641" s="4">
+        <v>12</v>
+      </c>
+      <c r="E641" s="4">
         <v>1</v>
       </c>
-      <c r="E641" s="6" t="inlineStr">
+      <c r="F641" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42116,9 +44042,12 @@
         </is>
       </c>
       <c r="D642" s="4">
+        <v>12</v>
+      </c>
+      <c r="E642" s="4">
         <v>2</v>
       </c>
-      <c r="E642" s="6" t="inlineStr">
+      <c r="F642" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42188,9 +44117,12 @@
         </is>
       </c>
       <c r="D643" s="4">
+        <v>12</v>
+      </c>
+      <c r="E643" s="4">
         <v>3</v>
       </c>
-      <c r="E643" s="6" t="inlineStr">
+      <c r="F643" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42260,9 +44192,12 @@
         </is>
       </c>
       <c r="D644" s="4">
+        <v>12</v>
+      </c>
+      <c r="E644" s="4">
         <v>4</v>
       </c>
-      <c r="E644" s="6" t="inlineStr">
+      <c r="F644" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42332,9 +44267,12 @@
         </is>
       </c>
       <c r="D645" s="4">
+        <v>12</v>
+      </c>
+      <c r="E645" s="4">
         <v>5</v>
       </c>
-      <c r="E645" s="6" t="inlineStr">
+      <c r="F645" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42404,9 +44342,12 @@
         </is>
       </c>
       <c r="D646" s="4">
+        <v>12</v>
+      </c>
+      <c r="E646" s="4">
         <v>6</v>
       </c>
-      <c r="E646" s="6" t="inlineStr">
+      <c r="F646" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42476,9 +44417,12 @@
         </is>
       </c>
       <c r="D647" s="4">
+        <v>12</v>
+      </c>
+      <c r="E647" s="4">
         <v>7</v>
       </c>
-      <c r="E647" s="6" t="inlineStr">
+      <c r="F647" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42548,9 +44492,12 @@
         </is>
       </c>
       <c r="D648" s="4">
+        <v>12</v>
+      </c>
+      <c r="E648" s="4">
         <v>8</v>
       </c>
-      <c r="E648" s="6" t="inlineStr">
+      <c r="F648" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42620,9 +44567,12 @@
         </is>
       </c>
       <c r="D649" s="4">
+        <v>12</v>
+      </c>
+      <c r="E649" s="4">
         <v>9</v>
       </c>
-      <c r="E649" s="6" t="inlineStr">
+      <c r="F649" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42692,9 +44642,12 @@
         </is>
       </c>
       <c r="D650" s="4">
+        <v>12</v>
+      </c>
+      <c r="E650" s="4">
         <v>10</v>
       </c>
-      <c r="E650" s="6" t="inlineStr">
+      <c r="F650" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42764,9 +44717,12 @@
         </is>
       </c>
       <c r="D651" s="4">
+        <v>12</v>
+      </c>
+      <c r="E651" s="4">
         <v>11</v>
       </c>
-      <c r="E651" s="6" t="inlineStr">
+      <c r="F651" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42838,7 +44794,10 @@
       <c r="D652" s="4">
         <v>12</v>
       </c>
-      <c r="E652" s="6" t="inlineStr">
+      <c r="E652" s="4">
+        <v>12</v>
+      </c>
+      <c r="F652" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42908,9 +44867,12 @@
         </is>
       </c>
       <c r="D653" s="4">
+        <v>5</v>
+      </c>
+      <c r="E653" s="4">
         <v>1</v>
       </c>
-      <c r="E653" s="6" t="inlineStr">
+      <c r="F653" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -42980,9 +44942,12 @@
         </is>
       </c>
       <c r="D654" s="4">
+        <v>5</v>
+      </c>
+      <c r="E654" s="4">
         <v>2</v>
       </c>
-      <c r="E654" s="6" t="inlineStr">
+      <c r="F654" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43052,9 +45017,12 @@
         </is>
       </c>
       <c r="D655" s="4">
+        <v>5</v>
+      </c>
+      <c r="E655" s="4">
         <v>3</v>
       </c>
-      <c r="E655" s="6" t="inlineStr">
+      <c r="F655" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43124,9 +45092,12 @@
         </is>
       </c>
       <c r="D656" s="4">
+        <v>5</v>
+      </c>
+      <c r="E656" s="4">
         <v>4</v>
       </c>
-      <c r="E656" s="6" t="inlineStr">
+      <c r="F656" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43198,7 +45169,10 @@
       <c r="D657" s="4">
         <v>5</v>
       </c>
-      <c r="E657" s="6" t="inlineStr">
+      <c r="E657" s="4">
+        <v>5</v>
+      </c>
+      <c r="F657" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43268,9 +45242,12 @@
         </is>
       </c>
       <c r="D658" s="4">
+        <v>2</v>
+      </c>
+      <c r="E658" s="4">
         <v>1</v>
       </c>
-      <c r="E658" s="6" t="inlineStr">
+      <c r="F658" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43342,7 +45319,10 @@
       <c r="D659" s="4">
         <v>2</v>
       </c>
-      <c r="E659" s="6" t="inlineStr">
+      <c r="E659" s="4">
+        <v>2</v>
+      </c>
+      <c r="F659" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43414,7 +45394,10 @@
       <c r="D660" s="4">
         <v>1</v>
       </c>
-      <c r="E660" s="6" t="inlineStr">
+      <c r="E660" s="4">
+        <v>1</v>
+      </c>
+      <c r="F660" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43486,7 +45469,10 @@
       <c r="D661" s="4">
         <v>1</v>
       </c>
-      <c r="E661" s="6" t="inlineStr">
+      <c r="E661" s="4">
+        <v>1</v>
+      </c>
+      <c r="F661" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -43540,370 +45526,491 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="363">
+  <mergeCells count="484">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="C2:C6"/>
+    <mergeCell ref="D2:D6"/>
     <mergeCell ref="A8:A12"/>
     <mergeCell ref="B8:B12"/>
     <mergeCell ref="C8:C12"/>
+    <mergeCell ref="D8:D12"/>
     <mergeCell ref="A13:A17"/>
     <mergeCell ref="B13:B17"/>
     <mergeCell ref="C13:C17"/>
+    <mergeCell ref="D13:D17"/>
     <mergeCell ref="A19:A22"/>
     <mergeCell ref="B19:B22"/>
     <mergeCell ref="C19:C22"/>
+    <mergeCell ref="D19:D22"/>
     <mergeCell ref="A23:A27"/>
     <mergeCell ref="B23:B27"/>
     <mergeCell ref="C23:C27"/>
+    <mergeCell ref="D23:D27"/>
     <mergeCell ref="A28:A31"/>
     <mergeCell ref="B28:B31"/>
     <mergeCell ref="C28:C31"/>
+    <mergeCell ref="D28:D31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="B32:B34"/>
     <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
     <mergeCell ref="A35:A37"/>
     <mergeCell ref="B35:B37"/>
     <mergeCell ref="C35:C37"/>
+    <mergeCell ref="D35:D37"/>
     <mergeCell ref="A40:A41"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
     <mergeCell ref="A45:A46"/>
     <mergeCell ref="B45:B46"/>
     <mergeCell ref="C45:C46"/>
+    <mergeCell ref="D45:D46"/>
     <mergeCell ref="A47:A50"/>
     <mergeCell ref="B47:B50"/>
     <mergeCell ref="C47:C50"/>
+    <mergeCell ref="D47:D50"/>
     <mergeCell ref="A51:A55"/>
     <mergeCell ref="B51:B55"/>
     <mergeCell ref="C51:C55"/>
+    <mergeCell ref="D51:D55"/>
     <mergeCell ref="A57:A61"/>
     <mergeCell ref="B57:B61"/>
     <mergeCell ref="C57:C61"/>
+    <mergeCell ref="D57:D61"/>
     <mergeCell ref="A67:A70"/>
     <mergeCell ref="B67:B70"/>
     <mergeCell ref="C67:C70"/>
+    <mergeCell ref="D67:D70"/>
     <mergeCell ref="A75:A79"/>
     <mergeCell ref="B75:B79"/>
     <mergeCell ref="C75:C79"/>
+    <mergeCell ref="D75:D79"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="B80:B81"/>
     <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
     <mergeCell ref="A82:A86"/>
     <mergeCell ref="B82:B86"/>
     <mergeCell ref="C82:C86"/>
+    <mergeCell ref="D82:D86"/>
     <mergeCell ref="A87:A91"/>
     <mergeCell ref="B87:B91"/>
     <mergeCell ref="C87:C91"/>
+    <mergeCell ref="D87:D91"/>
     <mergeCell ref="A92:A93"/>
     <mergeCell ref="B92:B93"/>
     <mergeCell ref="C92:C93"/>
+    <mergeCell ref="D92:D93"/>
     <mergeCell ref="A94:A98"/>
     <mergeCell ref="B94:B98"/>
     <mergeCell ref="C94:C98"/>
+    <mergeCell ref="D94:D98"/>
     <mergeCell ref="A99:A103"/>
     <mergeCell ref="B99:B103"/>
     <mergeCell ref="C99:C103"/>
+    <mergeCell ref="D99:D103"/>
     <mergeCell ref="A105:A109"/>
     <mergeCell ref="B105:B109"/>
     <mergeCell ref="C105:C109"/>
+    <mergeCell ref="D105:D109"/>
     <mergeCell ref="A110:A114"/>
     <mergeCell ref="B110:B114"/>
     <mergeCell ref="C110:C114"/>
+    <mergeCell ref="D110:D114"/>
     <mergeCell ref="A116:A120"/>
     <mergeCell ref="B116:B120"/>
     <mergeCell ref="C116:C120"/>
+    <mergeCell ref="D116:D120"/>
     <mergeCell ref="A124:A128"/>
     <mergeCell ref="B124:B128"/>
     <mergeCell ref="C124:C128"/>
+    <mergeCell ref="D124:D128"/>
     <mergeCell ref="A129:A132"/>
     <mergeCell ref="B129:B132"/>
     <mergeCell ref="C129:C132"/>
+    <mergeCell ref="D129:D132"/>
     <mergeCell ref="A133:A137"/>
     <mergeCell ref="B133:B137"/>
     <mergeCell ref="C133:C137"/>
+    <mergeCell ref="D133:D137"/>
     <mergeCell ref="A138:A142"/>
     <mergeCell ref="B138:B142"/>
     <mergeCell ref="C138:C142"/>
+    <mergeCell ref="D138:D142"/>
     <mergeCell ref="A143:A147"/>
     <mergeCell ref="B143:B147"/>
     <mergeCell ref="C143:C147"/>
+    <mergeCell ref="D143:D147"/>
     <mergeCell ref="A148:A152"/>
     <mergeCell ref="B148:B152"/>
     <mergeCell ref="C148:C152"/>
+    <mergeCell ref="D148:D152"/>
     <mergeCell ref="A153:A157"/>
     <mergeCell ref="B153:B157"/>
     <mergeCell ref="C153:C157"/>
+    <mergeCell ref="D153:D157"/>
     <mergeCell ref="A158:A162"/>
     <mergeCell ref="B158:B162"/>
     <mergeCell ref="C158:C162"/>
+    <mergeCell ref="D158:D162"/>
     <mergeCell ref="A163:A167"/>
     <mergeCell ref="B163:B167"/>
     <mergeCell ref="C163:C167"/>
+    <mergeCell ref="D163:D167"/>
     <mergeCell ref="A168:A172"/>
     <mergeCell ref="B168:B172"/>
     <mergeCell ref="C168:C172"/>
+    <mergeCell ref="D168:D172"/>
     <mergeCell ref="A174:A178"/>
     <mergeCell ref="B174:B178"/>
     <mergeCell ref="C174:C178"/>
+    <mergeCell ref="D174:D178"/>
     <mergeCell ref="A179:A183"/>
     <mergeCell ref="B179:B183"/>
     <mergeCell ref="C179:C183"/>
+    <mergeCell ref="D179:D183"/>
     <mergeCell ref="A188:A189"/>
     <mergeCell ref="B188:B189"/>
     <mergeCell ref="C188:C189"/>
+    <mergeCell ref="D188:D189"/>
     <mergeCell ref="A190:A192"/>
     <mergeCell ref="B190:B192"/>
     <mergeCell ref="C190:C192"/>
+    <mergeCell ref="D190:D192"/>
     <mergeCell ref="A197:A201"/>
     <mergeCell ref="B197:B201"/>
     <mergeCell ref="C197:C201"/>
+    <mergeCell ref="D197:D201"/>
     <mergeCell ref="A203:A207"/>
     <mergeCell ref="B203:B207"/>
     <mergeCell ref="C203:C207"/>
+    <mergeCell ref="D203:D207"/>
     <mergeCell ref="A208:A210"/>
     <mergeCell ref="B208:B210"/>
     <mergeCell ref="C208:C210"/>
+    <mergeCell ref="D208:D210"/>
     <mergeCell ref="A211:A214"/>
     <mergeCell ref="B211:B214"/>
     <mergeCell ref="C211:C214"/>
+    <mergeCell ref="D211:D214"/>
     <mergeCell ref="A215:A218"/>
     <mergeCell ref="B215:B218"/>
     <mergeCell ref="C215:C218"/>
+    <mergeCell ref="D215:D218"/>
     <mergeCell ref="A219:A221"/>
     <mergeCell ref="B219:B221"/>
     <mergeCell ref="C219:C221"/>
+    <mergeCell ref="D219:D221"/>
     <mergeCell ref="A222:A226"/>
     <mergeCell ref="B222:B226"/>
     <mergeCell ref="C222:C226"/>
+    <mergeCell ref="D222:D226"/>
     <mergeCell ref="A228:A230"/>
     <mergeCell ref="B228:B230"/>
     <mergeCell ref="C228:C230"/>
+    <mergeCell ref="D228:D230"/>
     <mergeCell ref="A232:A233"/>
     <mergeCell ref="B232:B233"/>
     <mergeCell ref="C232:C233"/>
+    <mergeCell ref="D232:D233"/>
     <mergeCell ref="A234:A237"/>
     <mergeCell ref="B234:B237"/>
     <mergeCell ref="C234:C237"/>
+    <mergeCell ref="D234:D237"/>
     <mergeCell ref="A239:A240"/>
     <mergeCell ref="B239:B240"/>
     <mergeCell ref="C239:C240"/>
+    <mergeCell ref="D239:D240"/>
     <mergeCell ref="A242:A243"/>
     <mergeCell ref="B242:B243"/>
     <mergeCell ref="C242:C243"/>
+    <mergeCell ref="D242:D243"/>
     <mergeCell ref="A246:A250"/>
     <mergeCell ref="B246:B250"/>
     <mergeCell ref="C246:C250"/>
+    <mergeCell ref="D246:D250"/>
     <mergeCell ref="A251:A252"/>
     <mergeCell ref="B251:B252"/>
     <mergeCell ref="C251:C252"/>
+    <mergeCell ref="D251:D252"/>
     <mergeCell ref="A253:A257"/>
     <mergeCell ref="B253:B257"/>
     <mergeCell ref="C253:C257"/>
+    <mergeCell ref="D253:D257"/>
     <mergeCell ref="A258:A262"/>
     <mergeCell ref="B258:B262"/>
     <mergeCell ref="C258:C262"/>
+    <mergeCell ref="D258:D262"/>
     <mergeCell ref="A263:A264"/>
     <mergeCell ref="B263:B264"/>
     <mergeCell ref="C263:C264"/>
+    <mergeCell ref="D263:D264"/>
     <mergeCell ref="A265:A269"/>
     <mergeCell ref="B265:B269"/>
     <mergeCell ref="C265:C269"/>
+    <mergeCell ref="D265:D269"/>
     <mergeCell ref="A270:A272"/>
     <mergeCell ref="B270:B272"/>
     <mergeCell ref="C270:C272"/>
+    <mergeCell ref="D270:D272"/>
     <mergeCell ref="A274:A275"/>
     <mergeCell ref="B274:B275"/>
     <mergeCell ref="C274:C275"/>
+    <mergeCell ref="D274:D275"/>
     <mergeCell ref="A277:A279"/>
     <mergeCell ref="B277:B279"/>
     <mergeCell ref="C277:C279"/>
+    <mergeCell ref="D277:D279"/>
     <mergeCell ref="A289:A290"/>
     <mergeCell ref="B289:B290"/>
     <mergeCell ref="C289:C290"/>
+    <mergeCell ref="D289:D290"/>
     <mergeCell ref="A294:A296"/>
     <mergeCell ref="B294:B296"/>
     <mergeCell ref="C294:C296"/>
+    <mergeCell ref="D294:D296"/>
     <mergeCell ref="A299:A302"/>
     <mergeCell ref="B299:B302"/>
     <mergeCell ref="C299:C302"/>
+    <mergeCell ref="D299:D302"/>
     <mergeCell ref="A303:A304"/>
     <mergeCell ref="B303:B304"/>
     <mergeCell ref="C303:C304"/>
+    <mergeCell ref="D303:D304"/>
     <mergeCell ref="A305:A309"/>
     <mergeCell ref="B305:B309"/>
     <mergeCell ref="C305:C309"/>
+    <mergeCell ref="D305:D309"/>
     <mergeCell ref="A310:A312"/>
     <mergeCell ref="B310:B312"/>
     <mergeCell ref="C310:C312"/>
+    <mergeCell ref="D310:D312"/>
     <mergeCell ref="A313:A314"/>
     <mergeCell ref="B313:B314"/>
     <mergeCell ref="C313:C314"/>
+    <mergeCell ref="D313:D314"/>
     <mergeCell ref="A321:A323"/>
     <mergeCell ref="B321:B323"/>
     <mergeCell ref="C321:C323"/>
+    <mergeCell ref="D321:D323"/>
     <mergeCell ref="A325:A327"/>
     <mergeCell ref="B325:B327"/>
     <mergeCell ref="C325:C327"/>
+    <mergeCell ref="D325:D327"/>
     <mergeCell ref="A329:A330"/>
     <mergeCell ref="B329:B330"/>
     <mergeCell ref="C329:C330"/>
+    <mergeCell ref="D329:D330"/>
     <mergeCell ref="A334:A335"/>
     <mergeCell ref="B334:B335"/>
     <mergeCell ref="C334:C335"/>
+    <mergeCell ref="D334:D335"/>
     <mergeCell ref="A338:A340"/>
     <mergeCell ref="B338:B340"/>
     <mergeCell ref="C338:C340"/>
+    <mergeCell ref="D338:D340"/>
     <mergeCell ref="A345:A346"/>
     <mergeCell ref="B345:B346"/>
     <mergeCell ref="C345:C346"/>
+    <mergeCell ref="D345:D346"/>
     <mergeCell ref="A347:A348"/>
     <mergeCell ref="B347:B348"/>
     <mergeCell ref="C347:C348"/>
+    <mergeCell ref="D347:D348"/>
     <mergeCell ref="A351:A352"/>
     <mergeCell ref="B351:B352"/>
     <mergeCell ref="C351:C352"/>
+    <mergeCell ref="D351:D352"/>
     <mergeCell ref="A353:A354"/>
     <mergeCell ref="B353:B354"/>
     <mergeCell ref="C353:C354"/>
+    <mergeCell ref="D353:D354"/>
     <mergeCell ref="A361:A366"/>
     <mergeCell ref="B361:B366"/>
     <mergeCell ref="C361:C366"/>
+    <mergeCell ref="D361:D366"/>
     <mergeCell ref="A367:A368"/>
     <mergeCell ref="B367:B368"/>
     <mergeCell ref="C367:C368"/>
+    <mergeCell ref="D367:D368"/>
     <mergeCell ref="A369:A370"/>
     <mergeCell ref="B369:B370"/>
     <mergeCell ref="C369:C370"/>
+    <mergeCell ref="D369:D370"/>
     <mergeCell ref="A372:A374"/>
     <mergeCell ref="B372:B374"/>
     <mergeCell ref="C372:C374"/>
+    <mergeCell ref="D372:D374"/>
     <mergeCell ref="A377:A383"/>
     <mergeCell ref="B377:B383"/>
     <mergeCell ref="C377:C383"/>
+    <mergeCell ref="D377:D383"/>
     <mergeCell ref="A384:A403"/>
     <mergeCell ref="B384:B403"/>
     <mergeCell ref="C384:C403"/>
+    <mergeCell ref="D384:D403"/>
     <mergeCell ref="A404:A409"/>
     <mergeCell ref="B404:B409"/>
     <mergeCell ref="C404:C409"/>
+    <mergeCell ref="D404:D409"/>
     <mergeCell ref="A410:A412"/>
     <mergeCell ref="B410:B412"/>
     <mergeCell ref="C410:C412"/>
+    <mergeCell ref="D410:D412"/>
     <mergeCell ref="A413:A419"/>
     <mergeCell ref="B413:B419"/>
     <mergeCell ref="C413:C419"/>
+    <mergeCell ref="D413:D419"/>
     <mergeCell ref="A420:A421"/>
     <mergeCell ref="B420:B421"/>
     <mergeCell ref="C420:C421"/>
+    <mergeCell ref="D420:D421"/>
     <mergeCell ref="A422:A423"/>
     <mergeCell ref="B422:B423"/>
     <mergeCell ref="C422:C423"/>
+    <mergeCell ref="D422:D423"/>
     <mergeCell ref="A424:A425"/>
     <mergeCell ref="B424:B425"/>
     <mergeCell ref="C424:C425"/>
+    <mergeCell ref="D424:D425"/>
     <mergeCell ref="A426:A428"/>
     <mergeCell ref="B426:B428"/>
     <mergeCell ref="C426:C428"/>
+    <mergeCell ref="D426:D428"/>
     <mergeCell ref="A429:A442"/>
     <mergeCell ref="B429:B442"/>
     <mergeCell ref="C429:C442"/>
+    <mergeCell ref="D429:D442"/>
     <mergeCell ref="A443:A447"/>
     <mergeCell ref="B443:B447"/>
     <mergeCell ref="C443:C447"/>
+    <mergeCell ref="D443:D447"/>
     <mergeCell ref="A448:A450"/>
     <mergeCell ref="B448:B450"/>
     <mergeCell ref="C448:C450"/>
+    <mergeCell ref="D448:D450"/>
     <mergeCell ref="A452:A471"/>
     <mergeCell ref="B452:B471"/>
     <mergeCell ref="C452:C471"/>
+    <mergeCell ref="D452:D471"/>
     <mergeCell ref="A472:A491"/>
     <mergeCell ref="B472:B491"/>
     <mergeCell ref="C472:C491"/>
+    <mergeCell ref="D472:D491"/>
     <mergeCell ref="A492:A501"/>
     <mergeCell ref="B492:B501"/>
     <mergeCell ref="C492:C501"/>
+    <mergeCell ref="D492:D501"/>
     <mergeCell ref="A503:A507"/>
     <mergeCell ref="B503:B507"/>
     <mergeCell ref="C503:C507"/>
+    <mergeCell ref="D503:D507"/>
     <mergeCell ref="A509:A512"/>
     <mergeCell ref="B509:B512"/>
     <mergeCell ref="C509:C512"/>
+    <mergeCell ref="D509:D512"/>
     <mergeCell ref="A514:A515"/>
     <mergeCell ref="B514:B515"/>
     <mergeCell ref="C514:C515"/>
+    <mergeCell ref="D514:D515"/>
     <mergeCell ref="A516:A517"/>
     <mergeCell ref="B516:B517"/>
     <mergeCell ref="C516:C517"/>
+    <mergeCell ref="D516:D517"/>
     <mergeCell ref="A520:A523"/>
     <mergeCell ref="B520:B523"/>
     <mergeCell ref="C520:C523"/>
+    <mergeCell ref="D520:D523"/>
     <mergeCell ref="A524:A529"/>
     <mergeCell ref="B524:B529"/>
     <mergeCell ref="C524:C529"/>
+    <mergeCell ref="D524:D529"/>
     <mergeCell ref="A531:A532"/>
     <mergeCell ref="B531:B532"/>
     <mergeCell ref="C531:C532"/>
+    <mergeCell ref="D531:D532"/>
     <mergeCell ref="A533:A536"/>
     <mergeCell ref="B533:B536"/>
     <mergeCell ref="C533:C536"/>
+    <mergeCell ref="D533:D536"/>
     <mergeCell ref="A539:A540"/>
     <mergeCell ref="B539:B540"/>
     <mergeCell ref="C539:C540"/>
+    <mergeCell ref="D539:D540"/>
     <mergeCell ref="A541:A543"/>
     <mergeCell ref="B541:B543"/>
     <mergeCell ref="C541:C543"/>
+    <mergeCell ref="D541:D543"/>
     <mergeCell ref="A546:A547"/>
     <mergeCell ref="B546:B547"/>
     <mergeCell ref="C546:C547"/>
+    <mergeCell ref="D546:D547"/>
     <mergeCell ref="A549:A554"/>
     <mergeCell ref="B549:B554"/>
     <mergeCell ref="C549:C554"/>
+    <mergeCell ref="D549:D554"/>
     <mergeCell ref="A555:A574"/>
     <mergeCell ref="B555:B574"/>
     <mergeCell ref="C555:C574"/>
+    <mergeCell ref="D555:D574"/>
     <mergeCell ref="A575:A582"/>
     <mergeCell ref="B575:B582"/>
     <mergeCell ref="C575:C582"/>
+    <mergeCell ref="D575:D582"/>
     <mergeCell ref="A583:A588"/>
     <mergeCell ref="B583:B588"/>
     <mergeCell ref="C583:C588"/>
+    <mergeCell ref="D583:D588"/>
     <mergeCell ref="A589:A595"/>
     <mergeCell ref="B589:B595"/>
     <mergeCell ref="C589:C595"/>
+    <mergeCell ref="D589:D595"/>
     <mergeCell ref="A596:A598"/>
     <mergeCell ref="B596:B598"/>
     <mergeCell ref="C596:C598"/>
+    <mergeCell ref="D596:D598"/>
     <mergeCell ref="A599:A602"/>
     <mergeCell ref="B599:B602"/>
     <mergeCell ref="C599:C602"/>
+    <mergeCell ref="D599:D602"/>
     <mergeCell ref="A603:A607"/>
     <mergeCell ref="B603:B607"/>
     <mergeCell ref="C603:C607"/>
+    <mergeCell ref="D603:D607"/>
     <mergeCell ref="A608:A610"/>
     <mergeCell ref="B608:B610"/>
     <mergeCell ref="C608:C610"/>
+    <mergeCell ref="D608:D610"/>
     <mergeCell ref="A611:A612"/>
     <mergeCell ref="B611:B612"/>
     <mergeCell ref="C611:C612"/>
+    <mergeCell ref="D611:D612"/>
     <mergeCell ref="A613:A615"/>
     <mergeCell ref="B613:B615"/>
     <mergeCell ref="C613:C615"/>
+    <mergeCell ref="D613:D615"/>
     <mergeCell ref="A616:A621"/>
     <mergeCell ref="B616:B621"/>
     <mergeCell ref="C616:C621"/>
+    <mergeCell ref="D616:D621"/>
     <mergeCell ref="A623:A640"/>
     <mergeCell ref="B623:B640"/>
     <mergeCell ref="C623:C640"/>
+    <mergeCell ref="D623:D640"/>
     <mergeCell ref="A641:A652"/>
     <mergeCell ref="B641:B652"/>
     <mergeCell ref="C641:C652"/>
+    <mergeCell ref="D641:D652"/>
     <mergeCell ref="A653:A657"/>
     <mergeCell ref="B653:B657"/>
     <mergeCell ref="C653:C657"/>
+    <mergeCell ref="D653:D657"/>
     <mergeCell ref="A658:A659"/>
     <mergeCell ref="B658:B659"/>
     <mergeCell ref="C658:C659"/>
+    <mergeCell ref="D658:D659"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
